--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,200 +656,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>16772900</v>
+        <v>21021300</v>
       </c>
       <c r="E8" s="3">
-        <v>13917100</v>
+        <v>17239400</v>
       </c>
       <c r="F8" s="3">
-        <v>14255700</v>
+        <v>14304100</v>
       </c>
       <c r="G8" s="3">
-        <v>20577800</v>
+        <v>14652200</v>
       </c>
       <c r="H8" s="3">
-        <v>19513400</v>
+        <v>21150100</v>
       </c>
       <c r="I8" s="3">
-        <v>18295100</v>
+        <v>20056000</v>
       </c>
       <c r="J8" s="3">
+        <v>18803900</v>
+      </c>
+      <c r="K8" s="3">
         <v>18553200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16076100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17906100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20106200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15721900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14648000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13352600</v>
+        <v>16405400</v>
       </c>
       <c r="E9" s="3">
-        <v>11267100</v>
+        <v>13723900</v>
       </c>
       <c r="F9" s="3">
-        <v>14487700</v>
+        <v>11580500</v>
       </c>
       <c r="G9" s="3">
-        <v>19409200</v>
+        <v>14890600</v>
       </c>
       <c r="H9" s="3">
-        <v>18027200</v>
+        <v>19948900</v>
       </c>
       <c r="I9" s="3">
-        <v>30815300</v>
+        <v>18528500</v>
       </c>
       <c r="J9" s="3">
+        <v>31672200</v>
+      </c>
+      <c r="K9" s="3">
         <v>14771800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12250600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13730700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32486900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12193800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11424500</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3420300</v>
+        <v>4615900</v>
       </c>
       <c r="E10" s="3">
-        <v>2649900</v>
+        <v>3515500</v>
       </c>
       <c r="F10" s="3">
-        <v>-232000</v>
+        <v>2723600</v>
       </c>
       <c r="G10" s="3">
-        <v>1168600</v>
+        <v>-238400</v>
       </c>
       <c r="H10" s="3">
-        <v>1486200</v>
+        <v>1201100</v>
       </c>
       <c r="I10" s="3">
-        <v>-12520100</v>
+        <v>1527600</v>
       </c>
       <c r="J10" s="3">
+        <v>-12868300</v>
+      </c>
+      <c r="K10" s="3">
         <v>3781300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3825500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4175400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-12380700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3528100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3223500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -866,50 +881,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>988800</v>
+        <v>828800</v>
       </c>
       <c r="E12" s="3">
-        <v>878300</v>
+        <v>1016300</v>
       </c>
       <c r="F12" s="3">
-        <v>798900</v>
+        <v>902800</v>
       </c>
       <c r="G12" s="3">
-        <v>790300</v>
+        <v>821200</v>
       </c>
       <c r="H12" s="3">
-        <v>802700</v>
+        <v>812200</v>
       </c>
       <c r="I12" s="3">
-        <v>861000</v>
+        <v>825000</v>
       </c>
       <c r="J12" s="3">
+        <v>884900</v>
+      </c>
+      <c r="K12" s="3">
         <v>956500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>797700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>870800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1658800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1447900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>609700</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -949,93 +968,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-100500</v>
+        <v>-1300</v>
       </c>
       <c r="E14" s="3">
-        <v>-69500</v>
+        <v>-103300</v>
       </c>
       <c r="F14" s="3">
-        <v>614100</v>
+        <v>-71400</v>
       </c>
       <c r="G14" s="3">
-        <v>-147600</v>
+        <v>631200</v>
       </c>
       <c r="H14" s="3">
-        <v>-435500</v>
+        <v>-151700</v>
       </c>
       <c r="I14" s="3">
-        <v>-973900</v>
+        <v>-447600</v>
       </c>
       <c r="J14" s="3">
+        <v>-1001000</v>
+      </c>
+      <c r="K14" s="3">
         <v>1215800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-473800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-903700</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>116600</v>
+        <v>113500</v>
       </c>
       <c r="E15" s="3">
-        <v>86800</v>
+        <v>119900</v>
       </c>
       <c r="F15" s="3">
-        <v>694700</v>
+        <v>89300</v>
       </c>
       <c r="G15" s="3">
-        <v>140200</v>
+        <v>714100</v>
       </c>
       <c r="H15" s="3">
-        <v>141400</v>
+        <v>144100</v>
       </c>
       <c r="I15" s="3">
-        <v>184800</v>
+        <v>145400</v>
       </c>
       <c r="J15" s="3">
+        <v>190000</v>
+      </c>
+      <c r="K15" s="3">
         <v>182400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>160500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>162900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>178500</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1049,92 +1077,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15634000</v>
+        <v>18541200</v>
       </c>
       <c r="E17" s="3">
-        <v>13211100</v>
+        <v>16068800</v>
       </c>
       <c r="F17" s="3">
-        <v>16719600</v>
+        <v>13578500</v>
       </c>
       <c r="G17" s="3">
-        <v>21462400</v>
+        <v>17184500</v>
       </c>
       <c r="H17" s="3">
-        <v>20509600</v>
+        <v>22059200</v>
       </c>
       <c r="I17" s="3">
-        <v>16867200</v>
+        <v>21080000</v>
       </c>
       <c r="J17" s="3">
+        <v>17336300</v>
+      </c>
+      <c r="K17" s="3">
         <v>18502300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14318000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16103200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17655100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13036700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13086300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1138900</v>
+        <v>2480100</v>
       </c>
       <c r="E18" s="3">
-        <v>705900</v>
+        <v>1170500</v>
       </c>
       <c r="F18" s="3">
-        <v>-2463800</v>
+        <v>725500</v>
       </c>
       <c r="G18" s="3">
-        <v>-884500</v>
+        <v>-2532300</v>
       </c>
       <c r="H18" s="3">
-        <v>-996200</v>
+        <v>-909100</v>
       </c>
       <c r="I18" s="3">
-        <v>1427900</v>
+        <v>-1023900</v>
       </c>
       <c r="J18" s="3">
+        <v>1467600</v>
+      </c>
+      <c r="K18" s="3">
         <v>50900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1758100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1802900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2451100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2685200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1561700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1151,218 +1186,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2576700</v>
+        <v>1085100</v>
       </c>
       <c r="E20" s="3">
-        <v>-758000</v>
+        <v>-2648400</v>
       </c>
       <c r="F20" s="3">
-        <v>-787800</v>
+        <v>-779100</v>
       </c>
       <c r="G20" s="3">
-        <v>5000</v>
+        <v>-809700</v>
       </c>
       <c r="H20" s="3">
-        <v>-2527100</v>
+        <v>5100</v>
       </c>
       <c r="I20" s="3">
-        <v>3491000</v>
+        <v>-2597400</v>
       </c>
       <c r="J20" s="3">
+        <v>3588100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5706800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1487600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1633400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-37100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>956700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-39500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-191100</v>
+        <v>4881900</v>
       </c>
       <c r="E21" s="3">
-        <v>1200900</v>
+        <v>-193100</v>
       </c>
       <c r="F21" s="3">
-        <v>-203000</v>
+        <v>1237600</v>
       </c>
       <c r="G21" s="3">
-        <v>753400</v>
+        <v>-200600</v>
       </c>
       <c r="H21" s="3">
-        <v>-2403200</v>
+        <v>778600</v>
       </c>
       <c r="I21" s="3">
-        <v>5896300</v>
+        <v>-2467100</v>
       </c>
       <c r="J21" s="3">
+        <v>6062800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4625200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1156300</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3">
         <v>4274900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2060100</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>425500</v>
+        <v>470500</v>
       </c>
       <c r="E22" s="3">
-        <v>312600</v>
+        <v>437400</v>
       </c>
       <c r="F22" s="3">
-        <v>220800</v>
+        <v>321300</v>
       </c>
       <c r="G22" s="3">
-        <v>225800</v>
+        <v>227000</v>
       </c>
       <c r="H22" s="3">
-        <v>132700</v>
+        <v>232100</v>
       </c>
       <c r="I22" s="3">
-        <v>83100</v>
+        <v>136400</v>
       </c>
       <c r="J22" s="3">
+        <v>85400</v>
+      </c>
+      <c r="K22" s="3">
         <v>95500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>82100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>79600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>65900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1863400</v>
+        <v>3094700</v>
       </c>
       <c r="E23" s="3">
-        <v>-364700</v>
+        <v>-1915200</v>
       </c>
       <c r="F23" s="3">
-        <v>-3472400</v>
+        <v>-374900</v>
       </c>
       <c r="G23" s="3">
-        <v>-1105400</v>
+        <v>-3569000</v>
       </c>
       <c r="H23" s="3">
-        <v>-3656000</v>
+        <v>-1136100</v>
       </c>
       <c r="I23" s="3">
-        <v>4835900</v>
+        <v>-3757700</v>
       </c>
       <c r="J23" s="3">
+        <v>4970300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5751400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>187400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>87300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2334400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3575900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1455100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-382100</v>
+        <v>29300</v>
       </c>
       <c r="E24" s="3">
-        <v>-518600</v>
+        <v>-392700</v>
       </c>
       <c r="F24" s="3">
-        <v>374700</v>
+        <v>-533000</v>
       </c>
       <c r="G24" s="3">
-        <v>521100</v>
+        <v>385100</v>
       </c>
       <c r="H24" s="3">
-        <v>-633900</v>
+        <v>535500</v>
       </c>
       <c r="I24" s="3">
-        <v>576900</v>
+        <v>-651600</v>
       </c>
       <c r="J24" s="3">
+        <v>592900</v>
+      </c>
+      <c r="K24" s="3">
         <v>-749300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>89000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>196800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>517700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>557200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>338400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1402,93 +1453,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1481300</v>
+        <v>3065300</v>
       </c>
       <c r="E26" s="3">
-        <v>153800</v>
+        <v>-1522500</v>
       </c>
       <c r="F26" s="3">
-        <v>-3847100</v>
+        <v>158100</v>
       </c>
       <c r="G26" s="3">
-        <v>-1626400</v>
+        <v>-3954100</v>
       </c>
       <c r="H26" s="3">
-        <v>-3022100</v>
+        <v>-1671700</v>
       </c>
       <c r="I26" s="3">
-        <v>4259000</v>
+        <v>-3106100</v>
       </c>
       <c r="J26" s="3">
+        <v>4377400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5002100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>98400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-109500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1816700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3018700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1116600</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1475100</v>
+        <v>3075500</v>
       </c>
       <c r="E27" s="3">
-        <v>152600</v>
+        <v>-1516100</v>
       </c>
       <c r="F27" s="3">
-        <v>-3848300</v>
+        <v>156800</v>
       </c>
       <c r="G27" s="3">
-        <v>-1631400</v>
+        <v>-3955400</v>
       </c>
       <c r="H27" s="3">
-        <v>-3032000</v>
+        <v>-1676800</v>
       </c>
       <c r="I27" s="3">
-        <v>4257700</v>
+        <v>-3116300</v>
       </c>
       <c r="J27" s="3">
+        <v>4376100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5002100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>97200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-95200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1119300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1528,51 +1588,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-99200</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-3700</v>
+        <v>-102000</v>
       </c>
       <c r="F29" s="3">
-        <v>-84400</v>
+        <v>-3800</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>-86700</v>
       </c>
       <c r="H29" s="3">
-        <v>53300</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-62000</v>
-      </c>
-      <c r="J29" s="3" t="s">
+        <v>54800</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>185100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>76900</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1612,9 +1678,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1654,93 +1723,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2576700</v>
+        <v>-1085100</v>
       </c>
       <c r="E32" s="3">
-        <v>758000</v>
+        <v>2648400</v>
       </c>
       <c r="F32" s="3">
-        <v>787800</v>
+        <v>779100</v>
       </c>
       <c r="G32" s="3">
-        <v>-5000</v>
+        <v>809700</v>
       </c>
       <c r="H32" s="3">
-        <v>2527100</v>
+        <v>-5100</v>
       </c>
       <c r="I32" s="3">
-        <v>-3491000</v>
+        <v>2597400</v>
       </c>
       <c r="J32" s="3">
+        <v>-3588100</v>
+      </c>
+      <c r="K32" s="3">
         <v>5706800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1487600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1633400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>37100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-956700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>39500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1574300</v>
+        <v>3075500</v>
       </c>
       <c r="E33" s="3">
-        <v>148900</v>
+        <v>-1618100</v>
       </c>
       <c r="F33" s="3">
-        <v>-3932700</v>
+        <v>153000</v>
       </c>
       <c r="G33" s="3">
-        <v>-1631400</v>
+        <v>-4042100</v>
       </c>
       <c r="H33" s="3">
-        <v>-2978700</v>
+        <v>-1676800</v>
       </c>
       <c r="I33" s="3">
-        <v>4195700</v>
+        <v>-3061500</v>
       </c>
       <c r="J33" s="3">
+        <v>4312400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5002100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>97200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>89900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1877200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1119300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1780,98 +1858,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1574300</v>
+        <v>3075500</v>
       </c>
       <c r="E35" s="3">
-        <v>148900</v>
+        <v>-1618100</v>
       </c>
       <c r="F35" s="3">
-        <v>-3932700</v>
+        <v>153000</v>
       </c>
       <c r="G35" s="3">
-        <v>-1631400</v>
+        <v>-4042100</v>
       </c>
       <c r="H35" s="3">
-        <v>-2978700</v>
+        <v>-1676800</v>
       </c>
       <c r="I35" s="3">
-        <v>4195700</v>
+        <v>-3061500</v>
       </c>
       <c r="J35" s="3">
+        <v>4312400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5002100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>97200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>89900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1877200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1119300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1888,8 +1975,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1906,386 +1994,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>801400</v>
+        <v>1959800</v>
       </c>
       <c r="E41" s="3">
-        <v>936700</v>
+        <v>823700</v>
       </c>
       <c r="F41" s="3">
-        <v>1818700</v>
+        <v>962700</v>
       </c>
       <c r="G41" s="3">
-        <v>2339800</v>
+        <v>1869300</v>
       </c>
       <c r="H41" s="3">
-        <v>2746700</v>
+        <v>2404800</v>
       </c>
       <c r="I41" s="3">
-        <v>5405300</v>
+        <v>2823100</v>
       </c>
       <c r="J41" s="3">
+        <v>5555600</v>
+      </c>
+      <c r="K41" s="3">
         <v>5162100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1667900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4112800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5086300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8082600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1706600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2154900</v>
+        <v>2509400</v>
       </c>
       <c r="E42" s="3">
-        <v>2214500</v>
+        <v>2214800</v>
       </c>
       <c r="F42" s="3">
-        <v>2286400</v>
+        <v>2276100</v>
       </c>
       <c r="G42" s="3">
-        <v>3152400</v>
+        <v>2350000</v>
       </c>
       <c r="H42" s="3">
-        <v>3393000</v>
+        <v>3240000</v>
       </c>
       <c r="I42" s="3">
-        <v>1896900</v>
+        <v>3487400</v>
       </c>
       <c r="J42" s="3">
+        <v>1949600</v>
+      </c>
+      <c r="K42" s="3">
         <v>1674800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2029900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>440800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1971500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>32900</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8294700</v>
+        <v>8766300</v>
       </c>
       <c r="E43" s="3">
-        <v>7371600</v>
+        <v>8525300</v>
       </c>
       <c r="F43" s="3">
-        <v>7670600</v>
+        <v>7576600</v>
       </c>
       <c r="G43" s="3">
-        <v>8181800</v>
+        <v>7883900</v>
       </c>
       <c r="H43" s="3">
-        <v>7676800</v>
+        <v>8409300</v>
       </c>
       <c r="I43" s="3">
-        <v>15443000</v>
+        <v>7890300</v>
       </c>
       <c r="J43" s="3">
+        <v>15872400</v>
+      </c>
+      <c r="K43" s="3">
         <v>15320200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7112100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7915400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6691600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15530500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5099900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5840700</v>
+        <v>6181700</v>
       </c>
       <c r="E44" s="3">
-        <v>4548000</v>
+        <v>6003200</v>
       </c>
       <c r="F44" s="3">
-        <v>4577800</v>
+        <v>4674500</v>
       </c>
       <c r="G44" s="3">
-        <v>5359400</v>
+        <v>4705100</v>
       </c>
       <c r="H44" s="3">
-        <v>5318500</v>
+        <v>5508400</v>
       </c>
       <c r="I44" s="3">
-        <v>9552600</v>
+        <v>5466400</v>
       </c>
       <c r="J44" s="3">
+        <v>9818300</v>
+      </c>
+      <c r="K44" s="3">
         <v>7988200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3088700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3437600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4557600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10572600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3372300</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2771500</v>
+        <v>3676100</v>
       </c>
       <c r="E45" s="3">
-        <v>1413000</v>
+        <v>2848600</v>
       </c>
       <c r="F45" s="3">
-        <v>1425400</v>
+        <v>1452300</v>
       </c>
       <c r="G45" s="3">
-        <v>883300</v>
+        <v>1465100</v>
       </c>
       <c r="H45" s="3">
-        <v>1731900</v>
+        <v>907900</v>
       </c>
       <c r="I45" s="3">
-        <v>339900</v>
+        <v>1780000</v>
       </c>
       <c r="J45" s="3">
+        <v>349400</v>
+      </c>
+      <c r="K45" s="3">
         <v>299000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>292800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>325900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>825300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>837700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>737400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19863200</v>
+        <v>23093300</v>
       </c>
       <c r="E46" s="3">
-        <v>16483900</v>
+        <v>20415600</v>
       </c>
       <c r="F46" s="3">
-        <v>17779000</v>
+        <v>16942300</v>
       </c>
       <c r="G46" s="3">
-        <v>19916600</v>
+        <v>18273500</v>
       </c>
       <c r="H46" s="3">
-        <v>20866900</v>
+        <v>20470500</v>
       </c>
       <c r="I46" s="3">
-        <v>16273000</v>
+        <v>21447200</v>
       </c>
       <c r="J46" s="3">
+        <v>16725500</v>
+      </c>
+      <c r="K46" s="3">
         <v>14548500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14191500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15794300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17601500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12401900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10949100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>568200</v>
+        <v>650300</v>
       </c>
       <c r="E47" s="3">
-        <v>545900</v>
+        <v>584000</v>
       </c>
       <c r="F47" s="3">
-        <v>512400</v>
+        <v>561000</v>
       </c>
       <c r="G47" s="3">
-        <v>535900</v>
+        <v>526600</v>
       </c>
       <c r="H47" s="3">
-        <v>538400</v>
+        <v>550800</v>
       </c>
       <c r="I47" s="3">
-        <v>497500</v>
+        <v>553400</v>
       </c>
       <c r="J47" s="3">
+        <v>511300</v>
+      </c>
+      <c r="K47" s="3">
         <v>735700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>713300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>793900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>862400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4669600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2225400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6199300</v>
+        <v>5907500</v>
       </c>
       <c r="E48" s="3">
-        <v>6351900</v>
+        <v>6371700</v>
       </c>
       <c r="F48" s="3">
-        <v>7344400</v>
+        <v>6528500</v>
       </c>
       <c r="G48" s="3">
-        <v>8451000</v>
+        <v>7548600</v>
       </c>
       <c r="H48" s="3">
-        <v>6114900</v>
+        <v>8686000</v>
       </c>
       <c r="I48" s="3">
-        <v>5778700</v>
+        <v>6285000</v>
       </c>
       <c r="J48" s="3">
+        <v>5939400</v>
+      </c>
+      <c r="K48" s="3">
         <v>10232500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4087800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4549500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4657900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9944300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3078700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5084000</v>
+        <v>5111900</v>
       </c>
       <c r="E49" s="3">
-        <v>5013300</v>
+        <v>5225400</v>
       </c>
       <c r="F49" s="3">
-        <v>6382900</v>
+        <v>5152700</v>
       </c>
       <c r="G49" s="3">
-        <v>6751300</v>
+        <v>6560400</v>
       </c>
       <c r="H49" s="3">
-        <v>6569000</v>
+        <v>6939100</v>
       </c>
       <c r="I49" s="3">
-        <v>6903900</v>
+        <v>6751700</v>
       </c>
       <c r="J49" s="3">
+        <v>7095900</v>
+      </c>
+      <c r="K49" s="3">
         <v>11408600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5440700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6055200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6848100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11251300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3795000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2325,9 +2441,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2367,51 +2486,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4821000</v>
+        <v>5417900</v>
       </c>
       <c r="E52" s="3">
-        <v>7178100</v>
+        <v>4955000</v>
       </c>
       <c r="F52" s="3">
-        <v>4600100</v>
+        <v>7377700</v>
       </c>
       <c r="G52" s="3">
-        <v>4374400</v>
+        <v>4728100</v>
       </c>
       <c r="H52" s="3">
-        <v>5432600</v>
+        <v>4496000</v>
       </c>
       <c r="I52" s="3">
-        <v>5193200</v>
+        <v>5583700</v>
       </c>
       <c r="J52" s="3">
+        <v>5337600</v>
+      </c>
+      <c r="K52" s="3">
         <v>4358200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1714800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1908500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1700000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3248800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1577500</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2451,51 +2576,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36535700</v>
+        <v>40181000</v>
       </c>
       <c r="E54" s="3">
-        <v>35573000</v>
+        <v>37551700</v>
       </c>
       <c r="F54" s="3">
-        <v>36618800</v>
+        <v>36562200</v>
       </c>
       <c r="G54" s="3">
-        <v>40029200</v>
+        <v>37637100</v>
       </c>
       <c r="H54" s="3">
-        <v>39521800</v>
+        <v>41142400</v>
       </c>
       <c r="I54" s="3">
-        <v>34646200</v>
+        <v>40620900</v>
       </c>
       <c r="J54" s="3">
+        <v>35609700</v>
+      </c>
+      <c r="K54" s="3">
         <v>29877400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26148100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29101300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31669900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23459300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21625600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2512,8 +2643,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2530,260 +2662,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2855900</v>
+        <v>2741500</v>
       </c>
       <c r="E57" s="3">
-        <v>2181000</v>
+        <v>2935300</v>
       </c>
       <c r="F57" s="3">
-        <v>2482400</v>
+        <v>2241600</v>
       </c>
       <c r="G57" s="3">
-        <v>3843400</v>
+        <v>2551500</v>
       </c>
       <c r="H57" s="3">
-        <v>3914100</v>
+        <v>3950300</v>
       </c>
       <c r="I57" s="3">
-        <v>17008600</v>
+        <v>4022900</v>
       </c>
       <c r="J57" s="3">
+        <v>17481600</v>
+      </c>
+      <c r="K57" s="3">
         <v>10398700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1867100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2077900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2143500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14007600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3773900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>444100</v>
+        <v>1031600</v>
       </c>
       <c r="E58" s="3">
-        <v>346100</v>
+        <v>456500</v>
       </c>
       <c r="F58" s="3">
-        <v>1578000</v>
+        <v>355800</v>
       </c>
       <c r="G58" s="3">
-        <v>961500</v>
+        <v>1621900</v>
       </c>
       <c r="H58" s="3">
-        <v>1064400</v>
+        <v>988200</v>
       </c>
       <c r="I58" s="3">
-        <v>203500</v>
+        <v>1094000</v>
       </c>
       <c r="J58" s="3">
+        <v>209100</v>
+      </c>
+      <c r="K58" s="3">
         <v>426800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>490800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>546200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>284300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>385300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>26300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13966700</v>
+        <v>15259100</v>
       </c>
       <c r="E59" s="3">
-        <v>11316800</v>
+        <v>14355100</v>
       </c>
       <c r="F59" s="3">
-        <v>12935700</v>
+        <v>11631500</v>
       </c>
       <c r="G59" s="3">
-        <v>13774400</v>
+        <v>13295500</v>
       </c>
       <c r="H59" s="3">
-        <v>13445600</v>
+        <v>14157400</v>
       </c>
       <c r="I59" s="3">
-        <v>18424200</v>
+        <v>13819500</v>
       </c>
       <c r="J59" s="3">
+        <v>18936500</v>
+      </c>
+      <c r="K59" s="3">
         <v>13970400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7215200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8030100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11002000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12483400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5306700</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>17266700</v>
+        <v>19032100</v>
       </c>
       <c r="E60" s="3">
-        <v>13843900</v>
+        <v>17746800</v>
       </c>
       <c r="F60" s="3">
-        <v>16996200</v>
+        <v>14228800</v>
       </c>
       <c r="G60" s="3">
-        <v>18579200</v>
+        <v>17468900</v>
       </c>
       <c r="H60" s="3">
-        <v>18424200</v>
+        <v>19095900</v>
       </c>
       <c r="I60" s="3">
-        <v>15421900</v>
+        <v>18936500</v>
       </c>
       <c r="J60" s="3">
+        <v>15850800</v>
+      </c>
+      <c r="K60" s="3">
         <v>13903400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9573000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10654200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13429800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9318600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9106900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6943600</v>
+        <v>6311700</v>
       </c>
       <c r="E61" s="3">
-        <v>9300800</v>
+        <v>7136700</v>
       </c>
       <c r="F61" s="3">
-        <v>7515600</v>
+        <v>9559400</v>
       </c>
       <c r="G61" s="3">
-        <v>6091300</v>
+        <v>7724600</v>
       </c>
       <c r="H61" s="3">
-        <v>4719200</v>
+        <v>6260700</v>
       </c>
       <c r="I61" s="3">
-        <v>4225500</v>
+        <v>4850500</v>
       </c>
       <c r="J61" s="3">
+        <v>4343000</v>
+      </c>
+      <c r="K61" s="3">
         <v>3951300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3376900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3758200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3465900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2135700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1559100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19788800</v>
+        <v>19394300</v>
       </c>
       <c r="E62" s="3">
-        <v>17282800</v>
+        <v>20339100</v>
       </c>
       <c r="F62" s="3">
-        <v>17872100</v>
+        <v>17763400</v>
       </c>
       <c r="G62" s="3">
-        <v>19501000</v>
+        <v>18369100</v>
       </c>
       <c r="H62" s="3">
-        <v>17217000</v>
+        <v>20043300</v>
       </c>
       <c r="I62" s="3">
-        <v>21879200</v>
+        <v>17695800</v>
       </c>
       <c r="J62" s="3">
+        <v>22487700</v>
+      </c>
+      <c r="K62" s="3">
         <v>25849100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7323000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8150000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6118900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8779500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5009100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2823,9 +2974,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2865,9 +3019,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2907,51 +3064,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>44041300</v>
+        <v>44874600</v>
       </c>
       <c r="E66" s="3">
-        <v>41356600</v>
+        <v>45266000</v>
       </c>
       <c r="F66" s="3">
-        <v>42694000</v>
+        <v>42506700</v>
       </c>
       <c r="G66" s="3">
-        <v>44217500</v>
+        <v>43881300</v>
       </c>
       <c r="H66" s="3">
-        <v>40854200</v>
+        <v>45447100</v>
       </c>
       <c r="I66" s="3">
-        <v>33492500</v>
+        <v>41990300</v>
       </c>
       <c r="J66" s="3">
+        <v>34423900</v>
+      </c>
+      <c r="K66" s="3">
         <v>33052100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20275200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22565100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23973200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15729600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15676400</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2968,8 +3131,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3009,9 +3173,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3051,9 +3218,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3093,9 +3263,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3135,51 +3308,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-11938300</v>
+        <v>-8955000</v>
       </c>
       <c r="E72" s="3">
-        <v>-9484400</v>
+        <v>-12270300</v>
       </c>
       <c r="F72" s="3">
-        <v>-9940900</v>
+        <v>-9748100</v>
       </c>
       <c r="G72" s="3">
-        <v>-5436300</v>
+        <v>-10217400</v>
       </c>
       <c r="H72" s="3">
-        <v>-3007200</v>
+        <v>-5587500</v>
       </c>
       <c r="I72" s="3">
-        <v>598000</v>
+        <v>-3090800</v>
       </c>
       <c r="J72" s="3">
+        <v>614600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-3690800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5349300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5953500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7163900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14793600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5456800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3219,9 +3398,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3261,9 +3443,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3303,51 +3488,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-7505600</v>
+        <v>-4693600</v>
       </c>
       <c r="E76" s="3">
-        <v>-5783700</v>
+        <v>-7714400</v>
       </c>
       <c r="F76" s="3">
-        <v>-6075200</v>
+        <v>-5944500</v>
       </c>
       <c r="G76" s="3">
-        <v>-4188300</v>
+        <v>-6244200</v>
       </c>
       <c r="H76" s="3">
-        <v>-1332400</v>
+        <v>-4304700</v>
       </c>
       <c r="I76" s="3">
-        <v>1153800</v>
+        <v>-1369500</v>
       </c>
       <c r="J76" s="3">
+        <v>1185800</v>
+      </c>
+      <c r="K76" s="3">
         <v>-3174700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5872900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6536200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7696700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7729700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5949300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3387,98 +3578,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1574300</v>
+        <v>3075500</v>
       </c>
       <c r="E81" s="3">
-        <v>148900</v>
+        <v>-1618100</v>
       </c>
       <c r="F81" s="3">
-        <v>-3932700</v>
+        <v>153000</v>
       </c>
       <c r="G81" s="3">
-        <v>-1631400</v>
+        <v>-4042100</v>
       </c>
       <c r="H81" s="3">
-        <v>-2978700</v>
+        <v>-1676800</v>
       </c>
       <c r="I81" s="3">
-        <v>4195700</v>
+        <v>-3061500</v>
       </c>
       <c r="J81" s="3">
+        <v>4312400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5002100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>97200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>89900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1877200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1119300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3495,50 +3695,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1245600</v>
+        <v>1312100</v>
       </c>
       <c r="E83" s="3">
-        <v>1251800</v>
+        <v>1280200</v>
       </c>
       <c r="F83" s="3">
-        <v>3045700</v>
+        <v>1286600</v>
       </c>
       <c r="G83" s="3">
-        <v>1631400</v>
+        <v>3130400</v>
       </c>
       <c r="H83" s="3">
-        <v>1119000</v>
+        <v>1676800</v>
       </c>
       <c r="I83" s="3">
-        <v>976400</v>
+        <v>1150100</v>
       </c>
       <c r="J83" s="3">
+        <v>1003500</v>
+      </c>
+      <c r="K83" s="3">
         <v>1029700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>913600</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O83" s="3">
         <v>629600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>539900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3578,9 +3782,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3620,9 +3827,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3662,9 +3872,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3704,9 +3917,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3746,51 +3962,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2295100</v>
+        <v>3168600</v>
       </c>
       <c r="E89" s="3">
-        <v>-321300</v>
+        <v>2358900</v>
       </c>
       <c r="F89" s="3">
-        <v>-3733000</v>
+        <v>-330300</v>
       </c>
       <c r="G89" s="3">
-        <v>2849700</v>
+        <v>-3836800</v>
       </c>
       <c r="H89" s="3">
-        <v>2761600</v>
+        <v>2928900</v>
       </c>
       <c r="I89" s="3">
-        <v>1875800</v>
+        <v>2838400</v>
       </c>
       <c r="J89" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="K89" s="3">
         <v>1750500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1281400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1696000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2801300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1622500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1719700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3807,50 +4029,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-445400</v>
+        <v>-547000</v>
       </c>
       <c r="E91" s="3">
-        <v>-406900</v>
+        <v>-457800</v>
       </c>
       <c r="F91" s="3">
+        <v>-418200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-745900</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-952500</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1154000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-930800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-725800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-926700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1122700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-905600</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-725800</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-570400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-844700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-918700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-562400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1020500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3890,9 +4116,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3932,51 +4161,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1024700</v>
+        <v>-925700</v>
       </c>
       <c r="E94" s="3">
-        <v>-531000</v>
+        <v>1053200</v>
       </c>
       <c r="F94" s="3">
-        <v>-1253000</v>
+        <v>-545700</v>
       </c>
       <c r="G94" s="3">
-        <v>-1138900</v>
+        <v>-1287900</v>
       </c>
       <c r="H94" s="3">
-        <v>-1209600</v>
+        <v>-1170500</v>
       </c>
       <c r="I94" s="3">
-        <v>-1431700</v>
+        <v>-1243200</v>
       </c>
       <c r="J94" s="3">
+        <v>-1471500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1690900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1165400</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O94" s="3">
         <v>548200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2906200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3993,8 +4228,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4034,9 +4270,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4076,9 +4315,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4118,9 +4360,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4160,133 +4405,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3555600</v>
+        <v>-700000</v>
       </c>
       <c r="E100" s="3">
-        <v>-109200</v>
+        <v>-3654400</v>
       </c>
       <c r="F100" s="3">
-        <v>3751600</v>
+        <v>-112200</v>
       </c>
       <c r="G100" s="3">
-        <v>-2223200</v>
+        <v>3855900</v>
       </c>
       <c r="H100" s="3">
-        <v>870900</v>
+        <v>-2285000</v>
       </c>
       <c r="I100" s="3">
-        <v>-157600</v>
+        <v>895100</v>
       </c>
       <c r="J100" s="3">
+        <v>-161900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-916800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>258900</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O100" s="3">
         <v>-427900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-862500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>193500</v>
+        <v>-107100</v>
       </c>
       <c r="E101" s="3">
-        <v>-101700</v>
+        <v>198900</v>
       </c>
       <c r="F101" s="3">
-        <v>69500</v>
+        <v>-104600</v>
       </c>
       <c r="G101" s="3">
-        <v>-129000</v>
+        <v>71400</v>
       </c>
       <c r="H101" s="3">
-        <v>81900</v>
+        <v>-132600</v>
       </c>
       <c r="I101" s="3">
-        <v>-85600</v>
+        <v>84200</v>
       </c>
       <c r="J101" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="K101" s="3">
         <v>354800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O101" s="3">
         <v>-69800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-42200</v>
+        <v>1435800</v>
       </c>
       <c r="E102" s="3">
-        <v>-1063200</v>
+        <v>-43400</v>
       </c>
       <c r="F102" s="3">
-        <v>-1164900</v>
+        <v>-1092800</v>
       </c>
       <c r="G102" s="3">
-        <v>-641400</v>
+        <v>-1197300</v>
       </c>
       <c r="H102" s="3">
-        <v>2504800</v>
+        <v>-659200</v>
       </c>
       <c r="I102" s="3">
-        <v>201000</v>
+        <v>2574400</v>
       </c>
       <c r="J102" s="3">
+        <v>206600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-502400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>367800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1466500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1925200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1672900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2054200</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -734,25 +734,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21021300</v>
+        <v>21095700</v>
       </c>
       <c r="E8" s="3">
-        <v>17239400</v>
+        <v>17300300</v>
       </c>
       <c r="F8" s="3">
-        <v>14304100</v>
+        <v>14354700</v>
       </c>
       <c r="G8" s="3">
-        <v>14652200</v>
+        <v>14704000</v>
       </c>
       <c r="H8" s="3">
-        <v>21150100</v>
+        <v>21224900</v>
       </c>
       <c r="I8" s="3">
-        <v>20056000</v>
+        <v>20127000</v>
       </c>
       <c r="J8" s="3">
-        <v>18803900</v>
+        <v>18870400</v>
       </c>
       <c r="K8" s="3">
         <v>18553200</v>
@@ -779,25 +779,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>16405400</v>
+        <v>16463500</v>
       </c>
       <c r="E9" s="3">
-        <v>13723900</v>
+        <v>13772400</v>
       </c>
       <c r="F9" s="3">
-        <v>11580500</v>
+        <v>11621400</v>
       </c>
       <c r="G9" s="3">
-        <v>14890600</v>
+        <v>14943300</v>
       </c>
       <c r="H9" s="3">
-        <v>19948900</v>
+        <v>20019500</v>
       </c>
       <c r="I9" s="3">
-        <v>18528500</v>
+        <v>18594000</v>
       </c>
       <c r="J9" s="3">
-        <v>31672200</v>
+        <v>31784200</v>
       </c>
       <c r="K9" s="3">
         <v>14771800</v>
@@ -824,25 +824,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4615900</v>
+        <v>4632200</v>
       </c>
       <c r="E10" s="3">
-        <v>3515500</v>
+        <v>3527900</v>
       </c>
       <c r="F10" s="3">
-        <v>2723600</v>
+        <v>2733200</v>
       </c>
       <c r="G10" s="3">
-        <v>-238400</v>
+        <v>-239300</v>
       </c>
       <c r="H10" s="3">
-        <v>1201100</v>
+        <v>1205400</v>
       </c>
       <c r="I10" s="3">
-        <v>1527600</v>
+        <v>1533000</v>
       </c>
       <c r="J10" s="3">
-        <v>-12868300</v>
+        <v>-12913800</v>
       </c>
       <c r="K10" s="3">
         <v>3781300</v>
@@ -888,25 +888,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>828800</v>
+        <v>831700</v>
       </c>
       <c r="E12" s="3">
-        <v>1016300</v>
+        <v>1019800</v>
       </c>
       <c r="F12" s="3">
-        <v>902800</v>
+        <v>906000</v>
       </c>
       <c r="G12" s="3">
-        <v>821200</v>
+        <v>824100</v>
       </c>
       <c r="H12" s="3">
-        <v>812200</v>
+        <v>815100</v>
       </c>
       <c r="I12" s="3">
-        <v>825000</v>
+        <v>827900</v>
       </c>
       <c r="J12" s="3">
-        <v>884900</v>
+        <v>888000</v>
       </c>
       <c r="K12" s="3">
         <v>956500</v>
@@ -981,22 +981,22 @@
         <v>-1300</v>
       </c>
       <c r="E14" s="3">
-        <v>-103300</v>
+        <v>-103600</v>
       </c>
       <c r="F14" s="3">
-        <v>-71400</v>
+        <v>-71700</v>
       </c>
       <c r="G14" s="3">
-        <v>631200</v>
+        <v>633400</v>
       </c>
       <c r="H14" s="3">
-        <v>-151700</v>
+        <v>-152300</v>
       </c>
       <c r="I14" s="3">
-        <v>-447600</v>
+        <v>-449100</v>
       </c>
       <c r="J14" s="3">
-        <v>-1001000</v>
+        <v>-1004500</v>
       </c>
       <c r="K14" s="3">
         <v>1215800</v>
@@ -1023,25 +1023,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>113500</v>
+        <v>113900</v>
       </c>
       <c r="E15" s="3">
-        <v>119900</v>
+        <v>120300</v>
       </c>
       <c r="F15" s="3">
-        <v>89300</v>
+        <v>89600</v>
       </c>
       <c r="G15" s="3">
-        <v>714100</v>
+        <v>716600</v>
       </c>
       <c r="H15" s="3">
-        <v>144100</v>
+        <v>144600</v>
       </c>
       <c r="I15" s="3">
-        <v>145400</v>
+        <v>145900</v>
       </c>
       <c r="J15" s="3">
-        <v>190000</v>
+        <v>190700</v>
       </c>
       <c r="K15" s="3">
         <v>182400</v>
@@ -1084,25 +1084,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18541200</v>
+        <v>18606800</v>
       </c>
       <c r="E17" s="3">
-        <v>16068800</v>
+        <v>16125600</v>
       </c>
       <c r="F17" s="3">
-        <v>13578500</v>
+        <v>13626600</v>
       </c>
       <c r="G17" s="3">
-        <v>17184500</v>
+        <v>17245300</v>
       </c>
       <c r="H17" s="3">
-        <v>22059200</v>
+        <v>22137300</v>
       </c>
       <c r="I17" s="3">
-        <v>21080000</v>
+        <v>21154500</v>
       </c>
       <c r="J17" s="3">
-        <v>17336300</v>
+        <v>17397600</v>
       </c>
       <c r="K17" s="3">
         <v>18502300</v>
@@ -1129,25 +1129,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2480100</v>
+        <v>2488800</v>
       </c>
       <c r="E18" s="3">
-        <v>1170500</v>
+        <v>1174700</v>
       </c>
       <c r="F18" s="3">
-        <v>725500</v>
+        <v>728100</v>
       </c>
       <c r="G18" s="3">
-        <v>-2532300</v>
+        <v>-2541300</v>
       </c>
       <c r="H18" s="3">
-        <v>-909100</v>
+        <v>-912400</v>
       </c>
       <c r="I18" s="3">
-        <v>-1023900</v>
+        <v>-1027500</v>
       </c>
       <c r="J18" s="3">
-        <v>1467600</v>
+        <v>1472800</v>
       </c>
       <c r="K18" s="3">
         <v>50900</v>
@@ -1193,25 +1193,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1085100</v>
+        <v>1088900</v>
       </c>
       <c r="E20" s="3">
-        <v>-2648400</v>
+        <v>-2657700</v>
       </c>
       <c r="F20" s="3">
-        <v>-779100</v>
+        <v>-781800</v>
       </c>
       <c r="G20" s="3">
-        <v>-809700</v>
+        <v>-812600</v>
       </c>
       <c r="H20" s="3">
         <v>5100</v>
       </c>
       <c r="I20" s="3">
-        <v>-2597400</v>
+        <v>-2606600</v>
       </c>
       <c r="J20" s="3">
-        <v>3588100</v>
+        <v>3600800</v>
       </c>
       <c r="K20" s="3">
         <v>-5706800</v>
@@ -1238,25 +1238,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4881900</v>
+        <v>4888700</v>
       </c>
       <c r="E21" s="3">
-        <v>-193100</v>
+        <v>-204000</v>
       </c>
       <c r="F21" s="3">
-        <v>1237600</v>
+        <v>1231700</v>
       </c>
       <c r="G21" s="3">
-        <v>-200600</v>
+        <v>-226200</v>
       </c>
       <c r="H21" s="3">
-        <v>778600</v>
+        <v>768100</v>
       </c>
       <c r="I21" s="3">
-        <v>-2467100</v>
+        <v>-2484900</v>
       </c>
       <c r="J21" s="3">
-        <v>6062800</v>
+        <v>6076300</v>
       </c>
       <c r="K21" s="3">
         <v>-4625200</v>
@@ -1283,25 +1283,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>470500</v>
+        <v>472200</v>
       </c>
       <c r="E22" s="3">
-        <v>437400</v>
+        <v>438900</v>
       </c>
       <c r="F22" s="3">
-        <v>321300</v>
+        <v>322500</v>
       </c>
       <c r="G22" s="3">
-        <v>227000</v>
+        <v>227800</v>
       </c>
       <c r="H22" s="3">
-        <v>232100</v>
+        <v>232900</v>
       </c>
       <c r="I22" s="3">
-        <v>136400</v>
+        <v>136900</v>
       </c>
       <c r="J22" s="3">
-        <v>85400</v>
+        <v>85700</v>
       </c>
       <c r="K22" s="3">
         <v>95500</v>
@@ -1328,25 +1328,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3094700</v>
+        <v>3105600</v>
       </c>
       <c r="E23" s="3">
-        <v>-1915200</v>
+        <v>-1922000</v>
       </c>
       <c r="F23" s="3">
-        <v>-374900</v>
+        <v>-376200</v>
       </c>
       <c r="G23" s="3">
-        <v>-3569000</v>
+        <v>-3581600</v>
       </c>
       <c r="H23" s="3">
-        <v>-1136100</v>
+        <v>-1140100</v>
       </c>
       <c r="I23" s="3">
-        <v>-3757700</v>
+        <v>-3771000</v>
       </c>
       <c r="J23" s="3">
-        <v>4970300</v>
+        <v>4987900</v>
       </c>
       <c r="K23" s="3">
         <v>-5751400</v>
@@ -1373,25 +1373,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="E24" s="3">
-        <v>-392700</v>
+        <v>-394100</v>
       </c>
       <c r="F24" s="3">
-        <v>-533000</v>
+        <v>-534900</v>
       </c>
       <c r="G24" s="3">
-        <v>385100</v>
+        <v>386400</v>
       </c>
       <c r="H24" s="3">
-        <v>535500</v>
+        <v>537400</v>
       </c>
       <c r="I24" s="3">
-        <v>-651600</v>
+        <v>-653900</v>
       </c>
       <c r="J24" s="3">
-        <v>592900</v>
+        <v>595000</v>
       </c>
       <c r="K24" s="3">
         <v>-749300</v>
@@ -1463,25 +1463,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3065300</v>
+        <v>3076200</v>
       </c>
       <c r="E26" s="3">
-        <v>-1522500</v>
+        <v>-1527900</v>
       </c>
       <c r="F26" s="3">
-        <v>158100</v>
+        <v>158700</v>
       </c>
       <c r="G26" s="3">
-        <v>-3954100</v>
+        <v>-3968100</v>
       </c>
       <c r="H26" s="3">
-        <v>-1671700</v>
+        <v>-1677600</v>
       </c>
       <c r="I26" s="3">
-        <v>-3106100</v>
+        <v>-3117100</v>
       </c>
       <c r="J26" s="3">
-        <v>4377400</v>
+        <v>4392900</v>
       </c>
       <c r="K26" s="3">
         <v>-5002100</v>
@@ -1508,25 +1508,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3075500</v>
+        <v>3086400</v>
       </c>
       <c r="E27" s="3">
-        <v>-1516100</v>
+        <v>-1521500</v>
       </c>
       <c r="F27" s="3">
-        <v>156800</v>
+        <v>157400</v>
       </c>
       <c r="G27" s="3">
-        <v>-3955400</v>
+        <v>-3969400</v>
       </c>
       <c r="H27" s="3">
-        <v>-1676800</v>
+        <v>-1682700</v>
       </c>
       <c r="I27" s="3">
-        <v>-3116300</v>
+        <v>-3127400</v>
       </c>
       <c r="J27" s="3">
-        <v>4376100</v>
+        <v>4391600</v>
       </c>
       <c r="K27" s="3">
         <v>-5002100</v>
@@ -1601,22 +1601,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-102000</v>
+        <v>-102400</v>
       </c>
       <c r="F29" s="3">
         <v>-3800</v>
       </c>
       <c r="G29" s="3">
-        <v>-86700</v>
+        <v>-87000</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>54800</v>
+        <v>55000</v>
       </c>
       <c r="J29" s="3">
-        <v>-63800</v>
+        <v>-64000</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1733,25 +1733,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1085100</v>
+        <v>-1088900</v>
       </c>
       <c r="E32" s="3">
-        <v>2648400</v>
+        <v>2657700</v>
       </c>
       <c r="F32" s="3">
-        <v>779100</v>
+        <v>781800</v>
       </c>
       <c r="G32" s="3">
-        <v>809700</v>
+        <v>812600</v>
       </c>
       <c r="H32" s="3">
         <v>-5100</v>
       </c>
       <c r="I32" s="3">
-        <v>2597400</v>
+        <v>2606600</v>
       </c>
       <c r="J32" s="3">
-        <v>-3588100</v>
+        <v>-3600800</v>
       </c>
       <c r="K32" s="3">
         <v>5706800</v>
@@ -1778,25 +1778,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3075500</v>
+        <v>3086400</v>
       </c>
       <c r="E33" s="3">
-        <v>-1618100</v>
+        <v>-1623800</v>
       </c>
       <c r="F33" s="3">
-        <v>153000</v>
+        <v>153600</v>
       </c>
       <c r="G33" s="3">
-        <v>-4042100</v>
+        <v>-4056400</v>
       </c>
       <c r="H33" s="3">
-        <v>-1676800</v>
+        <v>-1682700</v>
       </c>
       <c r="I33" s="3">
-        <v>-3061500</v>
+        <v>-3072300</v>
       </c>
       <c r="J33" s="3">
-        <v>4312400</v>
+        <v>4327600</v>
       </c>
       <c r="K33" s="3">
         <v>-5002100</v>
@@ -1868,25 +1868,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3075500</v>
+        <v>3086400</v>
       </c>
       <c r="E35" s="3">
-        <v>-1618100</v>
+        <v>-1623800</v>
       </c>
       <c r="F35" s="3">
-        <v>153000</v>
+        <v>153600</v>
       </c>
       <c r="G35" s="3">
-        <v>-4042100</v>
+        <v>-4056400</v>
       </c>
       <c r="H35" s="3">
-        <v>-1676800</v>
+        <v>-1682700</v>
       </c>
       <c r="I35" s="3">
-        <v>-3061500</v>
+        <v>-3072300</v>
       </c>
       <c r="J35" s="3">
-        <v>4312400</v>
+        <v>4327600</v>
       </c>
       <c r="K35" s="3">
         <v>-5002100</v>
@@ -2001,25 +2001,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1959800</v>
+        <v>1966800</v>
       </c>
       <c r="E41" s="3">
-        <v>823700</v>
+        <v>826600</v>
       </c>
       <c r="F41" s="3">
-        <v>962700</v>
+        <v>966100</v>
       </c>
       <c r="G41" s="3">
-        <v>1869300</v>
+        <v>1875900</v>
       </c>
       <c r="H41" s="3">
-        <v>2404800</v>
+        <v>2413300</v>
       </c>
       <c r="I41" s="3">
-        <v>2823100</v>
+        <v>2833100</v>
       </c>
       <c r="J41" s="3">
-        <v>5555600</v>
+        <v>5575300</v>
       </c>
       <c r="K41" s="3">
         <v>5162100</v>
@@ -2046,25 +2046,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2509400</v>
+        <v>2518300</v>
       </c>
       <c r="E42" s="3">
-        <v>2214800</v>
+        <v>2222700</v>
       </c>
       <c r="F42" s="3">
-        <v>2276100</v>
+        <v>2284100</v>
       </c>
       <c r="G42" s="3">
-        <v>2350000</v>
+        <v>2358300</v>
       </c>
       <c r="H42" s="3">
-        <v>3240000</v>
+        <v>3251500</v>
       </c>
       <c r="I42" s="3">
-        <v>3487400</v>
+        <v>3499700</v>
       </c>
       <c r="J42" s="3">
-        <v>1949600</v>
+        <v>1956500</v>
       </c>
       <c r="K42" s="3">
         <v>1674800</v>
@@ -2091,25 +2091,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8766300</v>
+        <v>8797300</v>
       </c>
       <c r="E43" s="3">
-        <v>8525300</v>
+        <v>8555500</v>
       </c>
       <c r="F43" s="3">
-        <v>7576600</v>
+        <v>7603400</v>
       </c>
       <c r="G43" s="3">
-        <v>7883900</v>
+        <v>7911800</v>
       </c>
       <c r="H43" s="3">
-        <v>8409300</v>
+        <v>8439000</v>
       </c>
       <c r="I43" s="3">
-        <v>7890300</v>
+        <v>7918200</v>
       </c>
       <c r="J43" s="3">
-        <v>15872400</v>
+        <v>15928600</v>
       </c>
       <c r="K43" s="3">
         <v>15320200</v>
@@ -2136,25 +2136,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6181700</v>
+        <v>6203500</v>
       </c>
       <c r="E44" s="3">
-        <v>6003200</v>
+        <v>6024400</v>
       </c>
       <c r="F44" s="3">
-        <v>4674500</v>
+        <v>4691100</v>
       </c>
       <c r="G44" s="3">
-        <v>4705100</v>
+        <v>4721800</v>
       </c>
       <c r="H44" s="3">
-        <v>5508400</v>
+        <v>5527900</v>
       </c>
       <c r="I44" s="3">
-        <v>5466400</v>
+        <v>5485700</v>
       </c>
       <c r="J44" s="3">
-        <v>9818300</v>
+        <v>9853000</v>
       </c>
       <c r="K44" s="3">
         <v>7988200</v>
@@ -2181,25 +2181,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3676100</v>
+        <v>3689100</v>
       </c>
       <c r="E45" s="3">
-        <v>2848600</v>
+        <v>2858600</v>
       </c>
       <c r="F45" s="3">
-        <v>1452300</v>
+        <v>1457500</v>
       </c>
       <c r="G45" s="3">
-        <v>1465100</v>
+        <v>1470300</v>
       </c>
       <c r="H45" s="3">
-        <v>907900</v>
+        <v>911100</v>
       </c>
       <c r="I45" s="3">
-        <v>1780000</v>
+        <v>1786300</v>
       </c>
       <c r="J45" s="3">
-        <v>349400</v>
+        <v>350600</v>
       </c>
       <c r="K45" s="3">
         <v>299000</v>
@@ -2226,25 +2226,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>23093300</v>
+        <v>23175000</v>
       </c>
       <c r="E46" s="3">
-        <v>20415600</v>
+        <v>20487800</v>
       </c>
       <c r="F46" s="3">
-        <v>16942300</v>
+        <v>17002200</v>
       </c>
       <c r="G46" s="3">
-        <v>18273500</v>
+        <v>18338100</v>
       </c>
       <c r="H46" s="3">
-        <v>20470500</v>
+        <v>20542900</v>
       </c>
       <c r="I46" s="3">
-        <v>21447200</v>
+        <v>21523000</v>
       </c>
       <c r="J46" s="3">
-        <v>16725500</v>
+        <v>16784600</v>
       </c>
       <c r="K46" s="3">
         <v>14548500</v>
@@ -2271,25 +2271,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>650300</v>
+        <v>652600</v>
       </c>
       <c r="E47" s="3">
-        <v>584000</v>
+        <v>586100</v>
       </c>
       <c r="F47" s="3">
-        <v>561000</v>
+        <v>563000</v>
       </c>
       <c r="G47" s="3">
-        <v>526600</v>
+        <v>528500</v>
       </c>
       <c r="H47" s="3">
-        <v>550800</v>
+        <v>552800</v>
       </c>
       <c r="I47" s="3">
-        <v>553400</v>
+        <v>555400</v>
       </c>
       <c r="J47" s="3">
-        <v>511300</v>
+        <v>513100</v>
       </c>
       <c r="K47" s="3">
         <v>735700</v>
@@ -2316,25 +2316,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5907500</v>
+        <v>5928400</v>
       </c>
       <c r="E48" s="3">
-        <v>6371700</v>
+        <v>6394200</v>
       </c>
       <c r="F48" s="3">
-        <v>6528500</v>
+        <v>6551600</v>
       </c>
       <c r="G48" s="3">
-        <v>7548600</v>
+        <v>7575300</v>
       </c>
       <c r="H48" s="3">
-        <v>8686000</v>
+        <v>8716700</v>
       </c>
       <c r="I48" s="3">
-        <v>6285000</v>
+        <v>6307200</v>
       </c>
       <c r="J48" s="3">
-        <v>5939400</v>
+        <v>5960400</v>
       </c>
       <c r="K48" s="3">
         <v>10232500</v>
@@ -2361,25 +2361,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5111900</v>
+        <v>5130000</v>
       </c>
       <c r="E49" s="3">
-        <v>5225400</v>
+        <v>5243800</v>
       </c>
       <c r="F49" s="3">
-        <v>5152700</v>
+        <v>5170900</v>
       </c>
       <c r="G49" s="3">
-        <v>6560400</v>
+        <v>6583600</v>
       </c>
       <c r="H49" s="3">
-        <v>6939100</v>
+        <v>6963600</v>
       </c>
       <c r="I49" s="3">
-        <v>6751700</v>
+        <v>6775500</v>
       </c>
       <c r="J49" s="3">
-        <v>7095900</v>
+        <v>7121000</v>
       </c>
       <c r="K49" s="3">
         <v>11408600</v>
@@ -2496,25 +2496,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5417900</v>
+        <v>5437100</v>
       </c>
       <c r="E52" s="3">
-        <v>4955000</v>
+        <v>4972600</v>
       </c>
       <c r="F52" s="3">
-        <v>7377700</v>
+        <v>7403800</v>
       </c>
       <c r="G52" s="3">
-        <v>4728100</v>
+        <v>4744800</v>
       </c>
       <c r="H52" s="3">
-        <v>4496000</v>
+        <v>4511900</v>
       </c>
       <c r="I52" s="3">
-        <v>5583700</v>
+        <v>5603400</v>
       </c>
       <c r="J52" s="3">
-        <v>5337600</v>
+        <v>5356400</v>
       </c>
       <c r="K52" s="3">
         <v>4358200</v>
@@ -2586,25 +2586,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>40181000</v>
+        <v>40323100</v>
       </c>
       <c r="E54" s="3">
-        <v>37551700</v>
+        <v>37684500</v>
       </c>
       <c r="F54" s="3">
-        <v>36562200</v>
+        <v>36691500</v>
       </c>
       <c r="G54" s="3">
-        <v>37637100</v>
+        <v>37770200</v>
       </c>
       <c r="H54" s="3">
-        <v>41142400</v>
+        <v>41287900</v>
       </c>
       <c r="I54" s="3">
-        <v>40620900</v>
+        <v>40764500</v>
       </c>
       <c r="J54" s="3">
-        <v>35609700</v>
+        <v>35735700</v>
       </c>
       <c r="K54" s="3">
         <v>29877400</v>
@@ -2669,25 +2669,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2741500</v>
+        <v>2751200</v>
       </c>
       <c r="E57" s="3">
-        <v>2935300</v>
+        <v>2945700</v>
       </c>
       <c r="F57" s="3">
-        <v>2241600</v>
+        <v>2249600</v>
       </c>
       <c r="G57" s="3">
-        <v>2551500</v>
+        <v>2560500</v>
       </c>
       <c r="H57" s="3">
-        <v>3950300</v>
+        <v>3964200</v>
       </c>
       <c r="I57" s="3">
-        <v>4022900</v>
+        <v>4037200</v>
       </c>
       <c r="J57" s="3">
-        <v>17481600</v>
+        <v>17543500</v>
       </c>
       <c r="K57" s="3">
         <v>10398700</v>
@@ -2714,25 +2714,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1031600</v>
+        <v>1035200</v>
       </c>
       <c r="E58" s="3">
-        <v>456500</v>
+        <v>458100</v>
       </c>
       <c r="F58" s="3">
-        <v>355800</v>
+        <v>357000</v>
       </c>
       <c r="G58" s="3">
-        <v>1621900</v>
+        <v>1627700</v>
       </c>
       <c r="H58" s="3">
-        <v>988200</v>
+        <v>991700</v>
       </c>
       <c r="I58" s="3">
-        <v>1094000</v>
+        <v>1097900</v>
       </c>
       <c r="J58" s="3">
-        <v>209100</v>
+        <v>209900</v>
       </c>
       <c r="K58" s="3">
         <v>426800</v>
@@ -2759,25 +2759,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15259100</v>
+        <v>15313100</v>
       </c>
       <c r="E59" s="3">
-        <v>14355100</v>
+        <v>14405800</v>
       </c>
       <c r="F59" s="3">
-        <v>11631500</v>
+        <v>11672600</v>
       </c>
       <c r="G59" s="3">
-        <v>13295500</v>
+        <v>13342500</v>
       </c>
       <c r="H59" s="3">
-        <v>14157400</v>
+        <v>14207500</v>
       </c>
       <c r="I59" s="3">
-        <v>13819500</v>
+        <v>13868400</v>
       </c>
       <c r="J59" s="3">
-        <v>18936500</v>
+        <v>19003500</v>
       </c>
       <c r="K59" s="3">
         <v>13970400</v>
@@ -2804,25 +2804,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>19032100</v>
+        <v>19099500</v>
       </c>
       <c r="E60" s="3">
-        <v>17746800</v>
+        <v>17809600</v>
       </c>
       <c r="F60" s="3">
-        <v>14228800</v>
+        <v>14279200</v>
       </c>
       <c r="G60" s="3">
-        <v>17468900</v>
+        <v>17530700</v>
       </c>
       <c r="H60" s="3">
-        <v>19095900</v>
+        <v>19163400</v>
       </c>
       <c r="I60" s="3">
-        <v>18936500</v>
+        <v>19003500</v>
       </c>
       <c r="J60" s="3">
-        <v>15850800</v>
+        <v>15906800</v>
       </c>
       <c r="K60" s="3">
         <v>13903400</v>
@@ -2849,25 +2849,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6311700</v>
+        <v>6334100</v>
       </c>
       <c r="E61" s="3">
-        <v>7136700</v>
+        <v>7162000</v>
       </c>
       <c r="F61" s="3">
-        <v>9559400</v>
+        <v>9593200</v>
       </c>
       <c r="G61" s="3">
-        <v>7724600</v>
+        <v>7751900</v>
       </c>
       <c r="H61" s="3">
-        <v>6260700</v>
+        <v>6282900</v>
       </c>
       <c r="I61" s="3">
-        <v>4850500</v>
+        <v>4867600</v>
       </c>
       <c r="J61" s="3">
-        <v>4343000</v>
+        <v>4358400</v>
       </c>
       <c r="K61" s="3">
         <v>3951300</v>
@@ -2894,25 +2894,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19394300</v>
+        <v>19462900</v>
       </c>
       <c r="E62" s="3">
-        <v>20339100</v>
+        <v>20411100</v>
       </c>
       <c r="F62" s="3">
-        <v>17763400</v>
+        <v>17826200</v>
       </c>
       <c r="G62" s="3">
-        <v>18369100</v>
+        <v>18434100</v>
       </c>
       <c r="H62" s="3">
-        <v>20043300</v>
+        <v>20114200</v>
       </c>
       <c r="I62" s="3">
-        <v>17695800</v>
+        <v>17758400</v>
       </c>
       <c r="J62" s="3">
-        <v>22487700</v>
+        <v>22567200</v>
       </c>
       <c r="K62" s="3">
         <v>25849100</v>
@@ -3074,25 +3074,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>44874600</v>
+        <v>45033300</v>
       </c>
       <c r="E66" s="3">
-        <v>45266000</v>
+        <v>45426200</v>
       </c>
       <c r="F66" s="3">
-        <v>42506700</v>
+        <v>42657100</v>
       </c>
       <c r="G66" s="3">
-        <v>43881300</v>
+        <v>44036500</v>
       </c>
       <c r="H66" s="3">
-        <v>45447100</v>
+        <v>45607900</v>
       </c>
       <c r="I66" s="3">
-        <v>41990300</v>
+        <v>42138800</v>
       </c>
       <c r="J66" s="3">
-        <v>34423900</v>
+        <v>34545600</v>
       </c>
       <c r="K66" s="3">
         <v>33052100</v>
@@ -3318,25 +3318,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-8955000</v>
+        <v>-8986700</v>
       </c>
       <c r="E72" s="3">
-        <v>-12270300</v>
+        <v>-12313700</v>
       </c>
       <c r="F72" s="3">
-        <v>-9748100</v>
+        <v>-9782600</v>
       </c>
       <c r="G72" s="3">
-        <v>-10217400</v>
+        <v>-10253500</v>
       </c>
       <c r="H72" s="3">
-        <v>-5587500</v>
+        <v>-5607300</v>
       </c>
       <c r="I72" s="3">
-        <v>-3090800</v>
+        <v>-3101800</v>
       </c>
       <c r="J72" s="3">
-        <v>614600</v>
+        <v>616800</v>
       </c>
       <c r="K72" s="3">
         <v>-3690800</v>
@@ -3498,25 +3498,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-4693600</v>
+        <v>-4710200</v>
       </c>
       <c r="E76" s="3">
-        <v>-7714400</v>
+        <v>-7741600</v>
       </c>
       <c r="F76" s="3">
-        <v>-5944500</v>
+        <v>-5965500</v>
       </c>
       <c r="G76" s="3">
-        <v>-6244200</v>
+        <v>-6266300</v>
       </c>
       <c r="H76" s="3">
-        <v>-4304700</v>
+        <v>-4320000</v>
       </c>
       <c r="I76" s="3">
-        <v>-1369500</v>
+        <v>-1374300</v>
       </c>
       <c r="J76" s="3">
-        <v>1185800</v>
+        <v>1190000</v>
       </c>
       <c r="K76" s="3">
         <v>-3174700</v>
@@ -3638,25 +3638,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3075500</v>
+        <v>3086400</v>
       </c>
       <c r="E81" s="3">
-        <v>-1618100</v>
+        <v>-1623800</v>
       </c>
       <c r="F81" s="3">
-        <v>153000</v>
+        <v>153600</v>
       </c>
       <c r="G81" s="3">
-        <v>-4042100</v>
+        <v>-4056400</v>
       </c>
       <c r="H81" s="3">
-        <v>-1676800</v>
+        <v>-1682700</v>
       </c>
       <c r="I81" s="3">
-        <v>-3061500</v>
+        <v>-3072300</v>
       </c>
       <c r="J81" s="3">
-        <v>4312400</v>
+        <v>4327600</v>
       </c>
       <c r="K81" s="3">
         <v>-5002100</v>
@@ -3702,25 +3702,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1312100</v>
+        <v>1316700</v>
       </c>
       <c r="E83" s="3">
-        <v>1280200</v>
+        <v>1284700</v>
       </c>
       <c r="F83" s="3">
-        <v>1286600</v>
+        <v>1291100</v>
       </c>
       <c r="G83" s="3">
-        <v>3130400</v>
+        <v>3141400</v>
       </c>
       <c r="H83" s="3">
-        <v>1676800</v>
+        <v>1682700</v>
       </c>
       <c r="I83" s="3">
-        <v>1150100</v>
+        <v>1154200</v>
       </c>
       <c r="J83" s="3">
-        <v>1003500</v>
+        <v>1007100</v>
       </c>
       <c r="K83" s="3">
         <v>1029700</v>
@@ -3972,25 +3972,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3168600</v>
+        <v>3179800</v>
       </c>
       <c r="E89" s="3">
-        <v>2358900</v>
+        <v>2367300</v>
       </c>
       <c r="F89" s="3">
-        <v>-330300</v>
+        <v>-331400</v>
       </c>
       <c r="G89" s="3">
-        <v>-3836800</v>
+        <v>-3850300</v>
       </c>
       <c r="H89" s="3">
-        <v>2928900</v>
+        <v>2939300</v>
       </c>
       <c r="I89" s="3">
-        <v>2838400</v>
+        <v>2848400</v>
       </c>
       <c r="J89" s="3">
-        <v>1928000</v>
+        <v>1934800</v>
       </c>
       <c r="K89" s="3">
         <v>1750500</v>
@@ -4036,25 +4036,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-547000</v>
+        <v>-549000</v>
       </c>
       <c r="E91" s="3">
-        <v>-457800</v>
+        <v>-459400</v>
       </c>
       <c r="F91" s="3">
-        <v>-418200</v>
+        <v>-419700</v>
       </c>
       <c r="G91" s="3">
-        <v>-745900</v>
+        <v>-748600</v>
       </c>
       <c r="H91" s="3">
-        <v>-952500</v>
+        <v>-955900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1154000</v>
+        <v>-1158000</v>
       </c>
       <c r="J91" s="3">
-        <v>-930800</v>
+        <v>-934100</v>
       </c>
       <c r="K91" s="3">
         <v>-725800</v>
@@ -4171,25 +4171,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-925700</v>
+        <v>-929000</v>
       </c>
       <c r="E94" s="3">
-        <v>1053200</v>
+        <v>1057000</v>
       </c>
       <c r="F94" s="3">
-        <v>-545700</v>
+        <v>-547700</v>
       </c>
       <c r="G94" s="3">
-        <v>-1287900</v>
+        <v>-1292400</v>
       </c>
       <c r="H94" s="3">
-        <v>-1170500</v>
+        <v>-1174700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1243200</v>
+        <v>-1247600</v>
       </c>
       <c r="J94" s="3">
-        <v>-1471500</v>
+        <v>-1476700</v>
       </c>
       <c r="K94" s="3">
         <v>-1690900</v>
@@ -4415,25 +4415,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-700000</v>
+        <v>-702500</v>
       </c>
       <c r="E100" s="3">
-        <v>-3654400</v>
+        <v>-3667400</v>
       </c>
       <c r="F100" s="3">
-        <v>-112200</v>
+        <v>-112600</v>
       </c>
       <c r="G100" s="3">
-        <v>3855900</v>
+        <v>3869500</v>
       </c>
       <c r="H100" s="3">
-        <v>-2285000</v>
+        <v>-2293100</v>
       </c>
       <c r="I100" s="3">
-        <v>895100</v>
+        <v>898300</v>
       </c>
       <c r="J100" s="3">
-        <v>-161900</v>
+        <v>-162500</v>
       </c>
       <c r="K100" s="3">
         <v>-916800</v>
@@ -4460,25 +4460,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-107100</v>
+        <v>-107500</v>
       </c>
       <c r="E101" s="3">
-        <v>198900</v>
+        <v>199600</v>
       </c>
       <c r="F101" s="3">
-        <v>-104600</v>
+        <v>-104900</v>
       </c>
       <c r="G101" s="3">
-        <v>71400</v>
+        <v>71700</v>
       </c>
       <c r="H101" s="3">
-        <v>-132600</v>
+        <v>-133100</v>
       </c>
       <c r="I101" s="3">
-        <v>84200</v>
+        <v>84500</v>
       </c>
       <c r="J101" s="3">
-        <v>-88000</v>
+        <v>-88300</v>
       </c>
       <c r="K101" s="3">
         <v>354800</v>
@@ -4505,25 +4505,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1435800</v>
+        <v>1440800</v>
       </c>
       <c r="E102" s="3">
-        <v>-43400</v>
+        <v>-43500</v>
       </c>
       <c r="F102" s="3">
-        <v>-1092800</v>
+        <v>-1096600</v>
       </c>
       <c r="G102" s="3">
-        <v>-1197300</v>
+        <v>-1201600</v>
       </c>
       <c r="H102" s="3">
-        <v>-659200</v>
+        <v>-661600</v>
       </c>
       <c r="I102" s="3">
-        <v>2574400</v>
+        <v>2583500</v>
       </c>
       <c r="J102" s="3">
-        <v>206600</v>
+        <v>207300</v>
       </c>
       <c r="K102" s="3">
         <v>-502400</v>

--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -663,9 +663,7 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -734,25 +732,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21095700</v>
+        <v>21632900</v>
       </c>
       <c r="E8" s="3">
-        <v>17300300</v>
+        <v>17740900</v>
       </c>
       <c r="F8" s="3">
-        <v>14354700</v>
+        <v>14720300</v>
       </c>
       <c r="G8" s="3">
-        <v>14704000</v>
+        <v>15078500</v>
       </c>
       <c r="H8" s="3">
-        <v>21224900</v>
+        <v>21765500</v>
       </c>
       <c r="I8" s="3">
-        <v>20127000</v>
+        <v>20639600</v>
       </c>
       <c r="J8" s="3">
-        <v>18870400</v>
+        <v>19351000</v>
       </c>
       <c r="K8" s="3">
         <v>18553200</v>
@@ -779,25 +777,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>16463500</v>
+        <v>16882800</v>
       </c>
       <c r="E9" s="3">
-        <v>13772400</v>
+        <v>14123200</v>
       </c>
       <c r="F9" s="3">
-        <v>11621400</v>
+        <v>11917400</v>
       </c>
       <c r="G9" s="3">
-        <v>14943300</v>
+        <v>15323900</v>
       </c>
       <c r="H9" s="3">
-        <v>20019500</v>
+        <v>20529400</v>
       </c>
       <c r="I9" s="3">
-        <v>18594000</v>
+        <v>19067600</v>
       </c>
       <c r="J9" s="3">
-        <v>31784200</v>
+        <v>32593700</v>
       </c>
       <c r="K9" s="3">
         <v>14771800</v>
@@ -824,25 +822,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4632200</v>
+        <v>4750200</v>
       </c>
       <c r="E10" s="3">
-        <v>3527900</v>
+        <v>3617700</v>
       </c>
       <c r="F10" s="3">
-        <v>2733200</v>
+        <v>2802900</v>
       </c>
       <c r="G10" s="3">
-        <v>-239300</v>
+        <v>-245400</v>
       </c>
       <c r="H10" s="3">
-        <v>1205400</v>
+        <v>1236100</v>
       </c>
       <c r="I10" s="3">
-        <v>1533000</v>
+        <v>1572000</v>
       </c>
       <c r="J10" s="3">
-        <v>-12913800</v>
+        <v>-13242700</v>
       </c>
       <c r="K10" s="3">
         <v>3781300</v>
@@ -888,25 +886,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>831700</v>
+        <v>852900</v>
       </c>
       <c r="E12" s="3">
-        <v>1019800</v>
+        <v>1045800</v>
       </c>
       <c r="F12" s="3">
-        <v>906000</v>
+        <v>929000</v>
       </c>
       <c r="G12" s="3">
-        <v>824100</v>
+        <v>845100</v>
       </c>
       <c r="H12" s="3">
-        <v>815100</v>
+        <v>835900</v>
       </c>
       <c r="I12" s="3">
-        <v>827900</v>
+        <v>849000</v>
       </c>
       <c r="J12" s="3">
-        <v>888000</v>
+        <v>910700</v>
       </c>
       <c r="K12" s="3">
         <v>956500</v>
@@ -981,22 +979,22 @@
         <v>-1300</v>
       </c>
       <c r="E14" s="3">
-        <v>-103600</v>
+        <v>-106300</v>
       </c>
       <c r="F14" s="3">
-        <v>-71700</v>
+        <v>-73500</v>
       </c>
       <c r="G14" s="3">
-        <v>633400</v>
+        <v>649500</v>
       </c>
       <c r="H14" s="3">
-        <v>-152300</v>
+        <v>-156200</v>
       </c>
       <c r="I14" s="3">
-        <v>-449100</v>
+        <v>-460600</v>
       </c>
       <c r="J14" s="3">
-        <v>-1004500</v>
+        <v>-1030100</v>
       </c>
       <c r="K14" s="3">
         <v>1215800</v>
@@ -1023,25 +1021,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>113900</v>
+        <v>116800</v>
       </c>
       <c r="E15" s="3">
-        <v>120300</v>
+        <v>123300</v>
       </c>
       <c r="F15" s="3">
-        <v>89600</v>
+        <v>91900</v>
       </c>
       <c r="G15" s="3">
-        <v>716600</v>
+        <v>734800</v>
       </c>
       <c r="H15" s="3">
-        <v>144600</v>
+        <v>148300</v>
       </c>
       <c r="I15" s="3">
-        <v>145900</v>
+        <v>149600</v>
       </c>
       <c r="J15" s="3">
-        <v>190700</v>
+        <v>195500</v>
       </c>
       <c r="K15" s="3">
         <v>182400</v>
@@ -1084,25 +1082,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18606800</v>
+        <v>19080700</v>
       </c>
       <c r="E17" s="3">
-        <v>16125600</v>
+        <v>16536300</v>
       </c>
       <c r="F17" s="3">
-        <v>13626600</v>
+        <v>13973600</v>
       </c>
       <c r="G17" s="3">
-        <v>17245300</v>
+        <v>17684500</v>
       </c>
       <c r="H17" s="3">
-        <v>22137300</v>
+        <v>22701100</v>
       </c>
       <c r="I17" s="3">
-        <v>21154500</v>
+        <v>21693300</v>
       </c>
       <c r="J17" s="3">
-        <v>17397600</v>
+        <v>17840700</v>
       </c>
       <c r="K17" s="3">
         <v>18502300</v>
@@ -1129,25 +1127,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2488800</v>
+        <v>2552200</v>
       </c>
       <c r="E18" s="3">
-        <v>1174700</v>
+        <v>1204600</v>
       </c>
       <c r="F18" s="3">
-        <v>728100</v>
+        <v>746600</v>
       </c>
       <c r="G18" s="3">
-        <v>-2541300</v>
+        <v>-2606000</v>
       </c>
       <c r="H18" s="3">
-        <v>-912400</v>
+        <v>-935600</v>
       </c>
       <c r="I18" s="3">
-        <v>-1027500</v>
+        <v>-1053700</v>
       </c>
       <c r="J18" s="3">
-        <v>1472800</v>
+        <v>1510300</v>
       </c>
       <c r="K18" s="3">
         <v>50900</v>
@@ -1193,25 +1191,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1088900</v>
+        <v>1116700</v>
       </c>
       <c r="E20" s="3">
-        <v>-2657700</v>
+        <v>-2725400</v>
       </c>
       <c r="F20" s="3">
-        <v>-781800</v>
+        <v>-801800</v>
       </c>
       <c r="G20" s="3">
-        <v>-812600</v>
+        <v>-833200</v>
       </c>
       <c r="H20" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="I20" s="3">
-        <v>-2606600</v>
+        <v>-2673000</v>
       </c>
       <c r="J20" s="3">
-        <v>3600800</v>
+        <v>3692500</v>
       </c>
       <c r="K20" s="3">
         <v>-5706800</v>
@@ -1238,25 +1236,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4888700</v>
+        <v>5019300</v>
       </c>
       <c r="E21" s="3">
-        <v>-204000</v>
+        <v>-203300</v>
       </c>
       <c r="F21" s="3">
-        <v>1231700</v>
+        <v>1269000</v>
       </c>
       <c r="G21" s="3">
-        <v>-226200</v>
+        <v>-217600</v>
       </c>
       <c r="H21" s="3">
-        <v>768100</v>
+        <v>795300</v>
       </c>
       <c r="I21" s="3">
-        <v>-2484900</v>
+        <v>-2543000</v>
       </c>
       <c r="J21" s="3">
-        <v>6076300</v>
+        <v>6235700</v>
       </c>
       <c r="K21" s="3">
         <v>-4625200</v>
@@ -1283,25 +1281,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>472200</v>
+        <v>484200</v>
       </c>
       <c r="E22" s="3">
-        <v>438900</v>
+        <v>450100</v>
       </c>
       <c r="F22" s="3">
-        <v>322500</v>
+        <v>330700</v>
       </c>
       <c r="G22" s="3">
-        <v>227800</v>
+        <v>233600</v>
       </c>
       <c r="H22" s="3">
-        <v>232900</v>
+        <v>238800</v>
       </c>
       <c r="I22" s="3">
-        <v>136900</v>
+        <v>140400</v>
       </c>
       <c r="J22" s="3">
-        <v>85700</v>
+        <v>87900</v>
       </c>
       <c r="K22" s="3">
         <v>95500</v>
@@ -1328,25 +1326,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3105600</v>
+        <v>3184700</v>
       </c>
       <c r="E23" s="3">
-        <v>-1922000</v>
+        <v>-1970900</v>
       </c>
       <c r="F23" s="3">
-        <v>-376200</v>
+        <v>-385800</v>
       </c>
       <c r="G23" s="3">
-        <v>-3581600</v>
+        <v>-3672800</v>
       </c>
       <c r="H23" s="3">
-        <v>-1140100</v>
+        <v>-1169200</v>
       </c>
       <c r="I23" s="3">
-        <v>-3771000</v>
+        <v>-3867100</v>
       </c>
       <c r="J23" s="3">
-        <v>4987900</v>
+        <v>5115000</v>
       </c>
       <c r="K23" s="3">
         <v>-5751400</v>
@@ -1373,25 +1371,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>29400</v>
+        <v>30200</v>
       </c>
       <c r="E24" s="3">
-        <v>-394100</v>
+        <v>-404200</v>
       </c>
       <c r="F24" s="3">
-        <v>-534900</v>
+        <v>-548500</v>
       </c>
       <c r="G24" s="3">
-        <v>386400</v>
+        <v>396300</v>
       </c>
       <c r="H24" s="3">
-        <v>537400</v>
+        <v>551100</v>
       </c>
       <c r="I24" s="3">
-        <v>-653900</v>
+        <v>-670500</v>
       </c>
       <c r="J24" s="3">
-        <v>595000</v>
+        <v>610200</v>
       </c>
       <c r="K24" s="3">
         <v>-749300</v>
@@ -1463,25 +1461,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3076200</v>
+        <v>3154500</v>
       </c>
       <c r="E26" s="3">
-        <v>-1527900</v>
+        <v>-1566800</v>
       </c>
       <c r="F26" s="3">
-        <v>158700</v>
+        <v>162700</v>
       </c>
       <c r="G26" s="3">
-        <v>-3968100</v>
+        <v>-4069100</v>
       </c>
       <c r="H26" s="3">
-        <v>-1677600</v>
+        <v>-1720300</v>
       </c>
       <c r="I26" s="3">
-        <v>-3117100</v>
+        <v>-3196500</v>
       </c>
       <c r="J26" s="3">
-        <v>4392900</v>
+        <v>4504800</v>
       </c>
       <c r="K26" s="3">
         <v>-5002100</v>
@@ -1508,25 +1506,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3086400</v>
+        <v>3165000</v>
       </c>
       <c r="E27" s="3">
-        <v>-1521500</v>
+        <v>-1560200</v>
       </c>
       <c r="F27" s="3">
-        <v>157400</v>
+        <v>161400</v>
       </c>
       <c r="G27" s="3">
-        <v>-3969400</v>
+        <v>-4070400</v>
       </c>
       <c r="H27" s="3">
-        <v>-1682700</v>
+        <v>-1725500</v>
       </c>
       <c r="I27" s="3">
-        <v>-3127400</v>
+        <v>-3207000</v>
       </c>
       <c r="J27" s="3">
-        <v>4391600</v>
+        <v>4503500</v>
       </c>
       <c r="K27" s="3">
         <v>-5002100</v>
@@ -1601,22 +1599,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-102400</v>
+        <v>-105000</v>
       </c>
       <c r="F29" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="G29" s="3">
-        <v>-87000</v>
+        <v>-89200</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>55000</v>
+        <v>56400</v>
       </c>
       <c r="J29" s="3">
-        <v>-64000</v>
+        <v>-65600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1733,25 +1731,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1088900</v>
+        <v>-1116700</v>
       </c>
       <c r="E32" s="3">
-        <v>2657700</v>
+        <v>2725400</v>
       </c>
       <c r="F32" s="3">
-        <v>781800</v>
+        <v>801800</v>
       </c>
       <c r="G32" s="3">
-        <v>812600</v>
+        <v>833200</v>
       </c>
       <c r="H32" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="I32" s="3">
-        <v>2606600</v>
+        <v>2673000</v>
       </c>
       <c r="J32" s="3">
-        <v>-3600800</v>
+        <v>-3692500</v>
       </c>
       <c r="K32" s="3">
         <v>5706800</v>
@@ -1778,25 +1776,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3086400</v>
+        <v>3165000</v>
       </c>
       <c r="E33" s="3">
-        <v>-1623800</v>
+        <v>-1665200</v>
       </c>
       <c r="F33" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="G33" s="3">
-        <v>-4056400</v>
+        <v>-4159700</v>
       </c>
       <c r="H33" s="3">
-        <v>-1682700</v>
+        <v>-1725500</v>
       </c>
       <c r="I33" s="3">
-        <v>-3072300</v>
+        <v>-3150600</v>
       </c>
       <c r="J33" s="3">
-        <v>4327600</v>
+        <v>4437900</v>
       </c>
       <c r="K33" s="3">
         <v>-5002100</v>
@@ -1868,25 +1866,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3086400</v>
+        <v>3165000</v>
       </c>
       <c r="E35" s="3">
-        <v>-1623800</v>
+        <v>-1665200</v>
       </c>
       <c r="F35" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="G35" s="3">
-        <v>-4056400</v>
+        <v>-4159700</v>
       </c>
       <c r="H35" s="3">
-        <v>-1682700</v>
+        <v>-1725500</v>
       </c>
       <c r="I35" s="3">
-        <v>-3072300</v>
+        <v>-3150600</v>
       </c>
       <c r="J35" s="3">
-        <v>4327600</v>
+        <v>4437900</v>
       </c>
       <c r="K35" s="3">
         <v>-5002100</v>
@@ -2001,25 +1999,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1966800</v>
+        <v>2016900</v>
       </c>
       <c r="E41" s="3">
-        <v>826600</v>
+        <v>847700</v>
       </c>
       <c r="F41" s="3">
-        <v>966100</v>
+        <v>990700</v>
       </c>
       <c r="G41" s="3">
-        <v>1875900</v>
+        <v>1923700</v>
       </c>
       <c r="H41" s="3">
-        <v>2413300</v>
+        <v>2474800</v>
       </c>
       <c r="I41" s="3">
-        <v>2833100</v>
+        <v>2905200</v>
       </c>
       <c r="J41" s="3">
-        <v>5575300</v>
+        <v>5717300</v>
       </c>
       <c r="K41" s="3">
         <v>5162100</v>
@@ -2046,25 +2044,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2518300</v>
+        <v>2582400</v>
       </c>
       <c r="E42" s="3">
-        <v>2222700</v>
+        <v>2279300</v>
       </c>
       <c r="F42" s="3">
-        <v>2284100</v>
+        <v>2342300</v>
       </c>
       <c r="G42" s="3">
-        <v>2358300</v>
+        <v>2418400</v>
       </c>
       <c r="H42" s="3">
-        <v>3251500</v>
+        <v>3334300</v>
       </c>
       <c r="I42" s="3">
-        <v>3499700</v>
+        <v>3588900</v>
       </c>
       <c r="J42" s="3">
-        <v>1956500</v>
+        <v>2006400</v>
       </c>
       <c r="K42" s="3">
         <v>1674800</v>
@@ -2091,25 +2089,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8797300</v>
+        <v>9021400</v>
       </c>
       <c r="E43" s="3">
-        <v>8555500</v>
+        <v>8773400</v>
       </c>
       <c r="F43" s="3">
-        <v>7603400</v>
+        <v>7797100</v>
       </c>
       <c r="G43" s="3">
-        <v>7911800</v>
+        <v>8113300</v>
       </c>
       <c r="H43" s="3">
-        <v>8439000</v>
+        <v>8654000</v>
       </c>
       <c r="I43" s="3">
-        <v>7918200</v>
+        <v>8119900</v>
       </c>
       <c r="J43" s="3">
-        <v>15928600</v>
+        <v>16334300</v>
       </c>
       <c r="K43" s="3">
         <v>15320200</v>
@@ -2136,25 +2134,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6203500</v>
+        <v>6361500</v>
       </c>
       <c r="E44" s="3">
-        <v>6024400</v>
+        <v>6177800</v>
       </c>
       <c r="F44" s="3">
-        <v>4691100</v>
+        <v>4810500</v>
       </c>
       <c r="G44" s="3">
-        <v>4721800</v>
+        <v>4842000</v>
       </c>
       <c r="H44" s="3">
-        <v>5527900</v>
+        <v>5668700</v>
       </c>
       <c r="I44" s="3">
-        <v>5485700</v>
+        <v>5625400</v>
       </c>
       <c r="J44" s="3">
-        <v>9853000</v>
+        <v>10103900</v>
       </c>
       <c r="K44" s="3">
         <v>7988200</v>
@@ -2181,25 +2179,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3689100</v>
+        <v>3783100</v>
       </c>
       <c r="E45" s="3">
-        <v>2858600</v>
+        <v>2931500</v>
       </c>
       <c r="F45" s="3">
-        <v>1457500</v>
+        <v>1494600</v>
       </c>
       <c r="G45" s="3">
-        <v>1470300</v>
+        <v>1507700</v>
       </c>
       <c r="H45" s="3">
-        <v>911100</v>
+        <v>934300</v>
       </c>
       <c r="I45" s="3">
-        <v>1786300</v>
+        <v>1831800</v>
       </c>
       <c r="J45" s="3">
-        <v>350600</v>
+        <v>359500</v>
       </c>
       <c r="K45" s="3">
         <v>299000</v>
@@ -2226,25 +2224,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>23175000</v>
+        <v>23765300</v>
       </c>
       <c r="E46" s="3">
-        <v>20487800</v>
+        <v>21009600</v>
       </c>
       <c r="F46" s="3">
-        <v>17002200</v>
+        <v>17435200</v>
       </c>
       <c r="G46" s="3">
-        <v>18338100</v>
+        <v>18805100</v>
       </c>
       <c r="H46" s="3">
-        <v>20542900</v>
+        <v>21066100</v>
       </c>
       <c r="I46" s="3">
-        <v>21523000</v>
+        <v>22071200</v>
       </c>
       <c r="J46" s="3">
-        <v>16784600</v>
+        <v>17212100</v>
       </c>
       <c r="K46" s="3">
         <v>14548500</v>
@@ -2271,25 +2269,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>652600</v>
+        <v>669200</v>
       </c>
       <c r="E47" s="3">
-        <v>586100</v>
+        <v>601000</v>
       </c>
       <c r="F47" s="3">
-        <v>563000</v>
+        <v>577400</v>
       </c>
       <c r="G47" s="3">
-        <v>528500</v>
+        <v>541900</v>
       </c>
       <c r="H47" s="3">
-        <v>552800</v>
+        <v>566900</v>
       </c>
       <c r="I47" s="3">
-        <v>555400</v>
+        <v>569500</v>
       </c>
       <c r="J47" s="3">
-        <v>513100</v>
+        <v>526200</v>
       </c>
       <c r="K47" s="3">
         <v>735700</v>
@@ -2316,25 +2314,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5928400</v>
+        <v>6079400</v>
       </c>
       <c r="E48" s="3">
-        <v>6394200</v>
+        <v>6557100</v>
       </c>
       <c r="F48" s="3">
-        <v>6551600</v>
+        <v>6718500</v>
       </c>
       <c r="G48" s="3">
-        <v>7575300</v>
+        <v>7768200</v>
       </c>
       <c r="H48" s="3">
-        <v>8716700</v>
+        <v>8938700</v>
       </c>
       <c r="I48" s="3">
-        <v>6307200</v>
+        <v>6467800</v>
       </c>
       <c r="J48" s="3">
-        <v>5960400</v>
+        <v>6112200</v>
       </c>
       <c r="K48" s="3">
         <v>10232500</v>
@@ -2361,25 +2359,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5130000</v>
+        <v>5260600</v>
       </c>
       <c r="E49" s="3">
-        <v>5243800</v>
+        <v>5377400</v>
       </c>
       <c r="F49" s="3">
-        <v>5170900</v>
+        <v>5302600</v>
       </c>
       <c r="G49" s="3">
-        <v>6583600</v>
+        <v>6751300</v>
       </c>
       <c r="H49" s="3">
-        <v>6963600</v>
+        <v>7141000</v>
       </c>
       <c r="I49" s="3">
-        <v>6775500</v>
+        <v>6948100</v>
       </c>
       <c r="J49" s="3">
-        <v>7121000</v>
+        <v>7302400</v>
       </c>
       <c r="K49" s="3">
         <v>11408600</v>
@@ -2496,25 +2494,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5437100</v>
+        <v>5575500</v>
       </c>
       <c r="E52" s="3">
-        <v>4972600</v>
+        <v>5099200</v>
       </c>
       <c r="F52" s="3">
-        <v>7403800</v>
+        <v>7592400</v>
       </c>
       <c r="G52" s="3">
-        <v>4744800</v>
+        <v>4865600</v>
       </c>
       <c r="H52" s="3">
-        <v>4511900</v>
+        <v>4626800</v>
       </c>
       <c r="I52" s="3">
-        <v>5603400</v>
+        <v>5746100</v>
       </c>
       <c r="J52" s="3">
-        <v>5356400</v>
+        <v>5492900</v>
       </c>
       <c r="K52" s="3">
         <v>4358200</v>
@@ -2586,25 +2584,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>40323100</v>
+        <v>41350000</v>
       </c>
       <c r="E54" s="3">
-        <v>37684500</v>
+        <v>38644300</v>
       </c>
       <c r="F54" s="3">
-        <v>36691500</v>
+        <v>37626000</v>
       </c>
       <c r="G54" s="3">
-        <v>37770200</v>
+        <v>38732200</v>
       </c>
       <c r="H54" s="3">
-        <v>41287900</v>
+        <v>42339400</v>
       </c>
       <c r="I54" s="3">
-        <v>40764500</v>
+        <v>41802800</v>
       </c>
       <c r="J54" s="3">
-        <v>35735700</v>
+        <v>36645800</v>
       </c>
       <c r="K54" s="3">
         <v>29877400</v>
@@ -2669,25 +2667,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2751200</v>
+        <v>2821200</v>
       </c>
       <c r="E57" s="3">
-        <v>2945700</v>
+        <v>3020700</v>
       </c>
       <c r="F57" s="3">
-        <v>2249600</v>
+        <v>2306800</v>
       </c>
       <c r="G57" s="3">
-        <v>2560500</v>
+        <v>2625700</v>
       </c>
       <c r="H57" s="3">
-        <v>3964200</v>
+        <v>4065200</v>
       </c>
       <c r="I57" s="3">
-        <v>4037200</v>
+        <v>4140000</v>
       </c>
       <c r="J57" s="3">
-        <v>17543500</v>
+        <v>17990300</v>
       </c>
       <c r="K57" s="3">
         <v>10398700</v>
@@ -2714,25 +2712,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1035200</v>
+        <v>1061600</v>
       </c>
       <c r="E58" s="3">
-        <v>458100</v>
+        <v>469800</v>
       </c>
       <c r="F58" s="3">
-        <v>357000</v>
+        <v>366100</v>
       </c>
       <c r="G58" s="3">
-        <v>1627700</v>
+        <v>1669100</v>
       </c>
       <c r="H58" s="3">
-        <v>991700</v>
+        <v>1017000</v>
       </c>
       <c r="I58" s="3">
-        <v>1097900</v>
+        <v>1125900</v>
       </c>
       <c r="J58" s="3">
-        <v>209900</v>
+        <v>215200</v>
       </c>
       <c r="K58" s="3">
         <v>426800</v>
@@ -2759,25 +2757,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15313100</v>
+        <v>15703100</v>
       </c>
       <c r="E59" s="3">
-        <v>14405800</v>
+        <v>14772700</v>
       </c>
       <c r="F59" s="3">
-        <v>11672600</v>
+        <v>11969900</v>
       </c>
       <c r="G59" s="3">
-        <v>13342500</v>
+        <v>13682300</v>
       </c>
       <c r="H59" s="3">
-        <v>14207500</v>
+        <v>14569400</v>
       </c>
       <c r="I59" s="3">
-        <v>13868400</v>
+        <v>14221600</v>
       </c>
       <c r="J59" s="3">
-        <v>19003500</v>
+        <v>19487500</v>
       </c>
       <c r="K59" s="3">
         <v>13970400</v>
@@ -2804,25 +2802,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>19099500</v>
+        <v>19585900</v>
       </c>
       <c r="E60" s="3">
-        <v>17809600</v>
+        <v>18263200</v>
       </c>
       <c r="F60" s="3">
-        <v>14279200</v>
+        <v>14642800</v>
       </c>
       <c r="G60" s="3">
-        <v>17530700</v>
+        <v>17977100</v>
       </c>
       <c r="H60" s="3">
-        <v>19163400</v>
+        <v>19651500</v>
       </c>
       <c r="I60" s="3">
-        <v>19003500</v>
+        <v>19487500</v>
       </c>
       <c r="J60" s="3">
-        <v>15906800</v>
+        <v>16312000</v>
       </c>
       <c r="K60" s="3">
         <v>13903400</v>
@@ -2849,25 +2847,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6334100</v>
+        <v>6495400</v>
       </c>
       <c r="E61" s="3">
-        <v>7162000</v>
+        <v>7344400</v>
       </c>
       <c r="F61" s="3">
-        <v>9593200</v>
+        <v>9837600</v>
       </c>
       <c r="G61" s="3">
-        <v>7751900</v>
+        <v>7949300</v>
       </c>
       <c r="H61" s="3">
-        <v>6282900</v>
+        <v>6442900</v>
       </c>
       <c r="I61" s="3">
-        <v>4867600</v>
+        <v>4991600</v>
       </c>
       <c r="J61" s="3">
-        <v>4358400</v>
+        <v>4469400</v>
       </c>
       <c r="K61" s="3">
         <v>3951300</v>
@@ -2894,25 +2892,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19462900</v>
+        <v>19958600</v>
       </c>
       <c r="E62" s="3">
-        <v>20411100</v>
+        <v>20930900</v>
       </c>
       <c r="F62" s="3">
-        <v>17826200</v>
+        <v>18280300</v>
       </c>
       <c r="G62" s="3">
-        <v>18434100</v>
+        <v>18903600</v>
       </c>
       <c r="H62" s="3">
-        <v>20114200</v>
+        <v>20626500</v>
       </c>
       <c r="I62" s="3">
-        <v>17758400</v>
+        <v>18210700</v>
       </c>
       <c r="J62" s="3">
-        <v>22567200</v>
+        <v>23142000</v>
       </c>
       <c r="K62" s="3">
         <v>25849100</v>
@@ -3074,25 +3072,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>45033300</v>
+        <v>46180300</v>
       </c>
       <c r="E66" s="3">
-        <v>45426200</v>
+        <v>46583100</v>
       </c>
       <c r="F66" s="3">
-        <v>42657100</v>
+        <v>43743500</v>
       </c>
       <c r="G66" s="3">
-        <v>44036500</v>
+        <v>45158100</v>
       </c>
       <c r="H66" s="3">
-        <v>45607900</v>
+        <v>46769400</v>
       </c>
       <c r="I66" s="3">
-        <v>42138800</v>
+        <v>43212100</v>
       </c>
       <c r="J66" s="3">
-        <v>34545600</v>
+        <v>35425500</v>
       </c>
       <c r="K66" s="3">
         <v>33052100</v>
@@ -3318,25 +3316,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-8986700</v>
+        <v>-9215600</v>
       </c>
       <c r="E72" s="3">
-        <v>-12313700</v>
+        <v>-12627300</v>
       </c>
       <c r="F72" s="3">
-        <v>-9782600</v>
+        <v>-10031800</v>
       </c>
       <c r="G72" s="3">
-        <v>-10253500</v>
+        <v>-10514700</v>
       </c>
       <c r="H72" s="3">
-        <v>-5607300</v>
+        <v>-5750100</v>
       </c>
       <c r="I72" s="3">
-        <v>-3101800</v>
+        <v>-3180800</v>
       </c>
       <c r="J72" s="3">
-        <v>616800</v>
+        <v>632500</v>
       </c>
       <c r="K72" s="3">
         <v>-3690800</v>
@@ -3498,25 +3496,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-4710200</v>
+        <v>-4830200</v>
       </c>
       <c r="E76" s="3">
-        <v>-7741600</v>
+        <v>-7938800</v>
       </c>
       <c r="F76" s="3">
-        <v>-5965500</v>
+        <v>-6117500</v>
       </c>
       <c r="G76" s="3">
-        <v>-6266300</v>
+        <v>-6425800</v>
       </c>
       <c r="H76" s="3">
-        <v>-4320000</v>
+        <v>-4430000</v>
       </c>
       <c r="I76" s="3">
-        <v>-1374300</v>
+        <v>-1409300</v>
       </c>
       <c r="J76" s="3">
-        <v>1190000</v>
+        <v>1220300</v>
       </c>
       <c r="K76" s="3">
         <v>-3174700</v>
@@ -3638,25 +3636,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3086400</v>
+        <v>3165000</v>
       </c>
       <c r="E81" s="3">
-        <v>-1623800</v>
+        <v>-1665200</v>
       </c>
       <c r="F81" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="G81" s="3">
-        <v>-4056400</v>
+        <v>-4159700</v>
       </c>
       <c r="H81" s="3">
-        <v>-1682700</v>
+        <v>-1725500</v>
       </c>
       <c r="I81" s="3">
-        <v>-3072300</v>
+        <v>-3150600</v>
       </c>
       <c r="J81" s="3">
-        <v>4327600</v>
+        <v>4437900</v>
       </c>
       <c r="K81" s="3">
         <v>-5002100</v>
@@ -3702,25 +3700,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1316700</v>
+        <v>1350300</v>
       </c>
       <c r="E83" s="3">
-        <v>1284700</v>
+        <v>1317400</v>
       </c>
       <c r="F83" s="3">
-        <v>1291100</v>
+        <v>1324000</v>
       </c>
       <c r="G83" s="3">
-        <v>3141400</v>
+        <v>3221500</v>
       </c>
       <c r="H83" s="3">
-        <v>1682700</v>
+        <v>1725500</v>
       </c>
       <c r="I83" s="3">
-        <v>1154200</v>
+        <v>1183600</v>
       </c>
       <c r="J83" s="3">
-        <v>1007100</v>
+        <v>1032700</v>
       </c>
       <c r="K83" s="3">
         <v>1029700</v>
@@ -3972,25 +3970,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3179800</v>
+        <v>3260800</v>
       </c>
       <c r="E89" s="3">
-        <v>2367300</v>
+        <v>2427600</v>
       </c>
       <c r="F89" s="3">
-        <v>-331400</v>
+        <v>-339900</v>
       </c>
       <c r="G89" s="3">
-        <v>-3850300</v>
+        <v>-3948400</v>
       </c>
       <c r="H89" s="3">
-        <v>2939300</v>
+        <v>3014100</v>
       </c>
       <c r="I89" s="3">
-        <v>2848400</v>
+        <v>2921000</v>
       </c>
       <c r="J89" s="3">
-        <v>1934800</v>
+        <v>1984000</v>
       </c>
       <c r="K89" s="3">
         <v>1750500</v>
@@ -4036,25 +4034,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-549000</v>
+        <v>-562900</v>
       </c>
       <c r="E91" s="3">
-        <v>-459400</v>
+        <v>-471100</v>
       </c>
       <c r="F91" s="3">
-        <v>-419700</v>
+        <v>-430400</v>
       </c>
       <c r="G91" s="3">
-        <v>-748600</v>
+        <v>-767600</v>
       </c>
       <c r="H91" s="3">
-        <v>-955900</v>
+        <v>-980200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1158000</v>
+        <v>-1187500</v>
       </c>
       <c r="J91" s="3">
-        <v>-934100</v>
+        <v>-957900</v>
       </c>
       <c r="K91" s="3">
         <v>-725800</v>
@@ -4171,25 +4169,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-929000</v>
+        <v>-952700</v>
       </c>
       <c r="E94" s="3">
-        <v>1057000</v>
+        <v>1083900</v>
       </c>
       <c r="F94" s="3">
-        <v>-547700</v>
+        <v>-561600</v>
       </c>
       <c r="G94" s="3">
-        <v>-1292400</v>
+        <v>-1325300</v>
       </c>
       <c r="H94" s="3">
-        <v>-1174700</v>
+        <v>-1204600</v>
       </c>
       <c r="I94" s="3">
-        <v>-1247600</v>
+        <v>-1279400</v>
       </c>
       <c r="J94" s="3">
-        <v>-1476700</v>
+        <v>-1514300</v>
       </c>
       <c r="K94" s="3">
         <v>-1690900</v>
@@ -4415,25 +4413,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-702500</v>
+        <v>-720400</v>
       </c>
       <c r="E100" s="3">
-        <v>-3667400</v>
+        <v>-3760800</v>
       </c>
       <c r="F100" s="3">
-        <v>-112600</v>
+        <v>-115500</v>
       </c>
       <c r="G100" s="3">
-        <v>3869500</v>
+        <v>3968100</v>
       </c>
       <c r="H100" s="3">
-        <v>-2293100</v>
+        <v>-2351500</v>
       </c>
       <c r="I100" s="3">
-        <v>898300</v>
+        <v>921200</v>
       </c>
       <c r="J100" s="3">
-        <v>-162500</v>
+        <v>-166600</v>
       </c>
       <c r="K100" s="3">
         <v>-916800</v>
@@ -4460,25 +4458,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-107500</v>
+        <v>-110200</v>
       </c>
       <c r="E101" s="3">
-        <v>199600</v>
+        <v>204700</v>
       </c>
       <c r="F101" s="3">
-        <v>-104900</v>
+        <v>-107600</v>
       </c>
       <c r="G101" s="3">
-        <v>71700</v>
+        <v>73500</v>
       </c>
       <c r="H101" s="3">
-        <v>-133100</v>
+        <v>-136500</v>
       </c>
       <c r="I101" s="3">
-        <v>84500</v>
+        <v>86600</v>
       </c>
       <c r="J101" s="3">
-        <v>-88300</v>
+        <v>-90500</v>
       </c>
       <c r="K101" s="3">
         <v>354800</v>
@@ -4505,25 +4503,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1440800</v>
+        <v>1477500</v>
       </c>
       <c r="E102" s="3">
-        <v>-43500</v>
+        <v>-44600</v>
       </c>
       <c r="F102" s="3">
-        <v>-1096600</v>
+        <v>-1124600</v>
       </c>
       <c r="G102" s="3">
-        <v>-1201600</v>
+        <v>-1232200</v>
       </c>
       <c r="H102" s="3">
-        <v>-661600</v>
+        <v>-678400</v>
       </c>
       <c r="I102" s="3">
-        <v>2583500</v>
+        <v>2649300</v>
       </c>
       <c r="J102" s="3">
-        <v>207300</v>
+        <v>212600</v>
       </c>
       <c r="K102" s="3">
         <v>-502400</v>

--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -664,9 +664,7 @@
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
@@ -732,25 +730,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21632900</v>
+        <v>20999100</v>
       </c>
       <c r="E8" s="3">
-        <v>17740900</v>
+        <v>16290100</v>
       </c>
       <c r="F8" s="3">
-        <v>14720300</v>
+        <v>15189800</v>
       </c>
       <c r="G8" s="3">
-        <v>15078500</v>
+        <v>15688700</v>
       </c>
       <c r="H8" s="3">
-        <v>21765500</v>
+        <v>21968100</v>
       </c>
       <c r="I8" s="3">
-        <v>20639600</v>
+        <v>20046900</v>
       </c>
       <c r="J8" s="3">
-        <v>19351000</v>
+        <v>19932400</v>
       </c>
       <c r="K8" s="3">
         <v>18553200</v>
@@ -777,25 +775,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>16882800</v>
+        <v>16355000</v>
       </c>
       <c r="E9" s="3">
-        <v>14123200</v>
+        <v>13053800</v>
       </c>
       <c r="F9" s="3">
-        <v>11917400</v>
+        <v>12297600</v>
       </c>
       <c r="G9" s="3">
-        <v>15323900</v>
+        <v>14169100</v>
       </c>
       <c r="H9" s="3">
-        <v>20529400</v>
+        <v>20720500</v>
       </c>
       <c r="I9" s="3">
-        <v>19067600</v>
+        <v>18520000</v>
       </c>
       <c r="J9" s="3">
-        <v>32593700</v>
+        <v>16658800</v>
       </c>
       <c r="K9" s="3">
         <v>14771800</v>
@@ -822,25 +820,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4750200</v>
+        <v>4644100</v>
       </c>
       <c r="E10" s="3">
-        <v>3617700</v>
+        <v>3236300</v>
       </c>
       <c r="F10" s="3">
-        <v>2802900</v>
+        <v>2892300</v>
       </c>
       <c r="G10" s="3">
-        <v>-245400</v>
+        <v>1519600</v>
       </c>
       <c r="H10" s="3">
-        <v>1236100</v>
+        <v>1247600</v>
       </c>
       <c r="I10" s="3">
-        <v>1572000</v>
+        <v>1526900</v>
       </c>
       <c r="J10" s="3">
-        <v>-13242700</v>
+        <v>3273600</v>
       </c>
       <c r="K10" s="3">
         <v>3781300</v>
@@ -886,25 +884,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>852900</v>
+        <v>941300</v>
       </c>
       <c r="E12" s="3">
-        <v>1045800</v>
+        <v>1073600</v>
       </c>
       <c r="F12" s="3">
-        <v>929000</v>
+        <v>1053500</v>
       </c>
       <c r="G12" s="3">
-        <v>845100</v>
+        <v>987100</v>
       </c>
       <c r="H12" s="3">
-        <v>835900</v>
+        <v>1019800</v>
       </c>
       <c r="I12" s="3">
-        <v>849000</v>
+        <v>978800</v>
       </c>
       <c r="J12" s="3">
-        <v>910700</v>
+        <v>1139400</v>
       </c>
       <c r="K12" s="3">
         <v>956500</v>
@@ -976,25 +974,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-1300</v>
+        <v>-639400</v>
       </c>
       <c r="E14" s="3">
-        <v>-106300</v>
+        <v>2123000</v>
       </c>
       <c r="F14" s="3">
-        <v>-73500</v>
+        <v>652700</v>
       </c>
       <c r="G14" s="3">
-        <v>649500</v>
+        <v>2566800</v>
       </c>
       <c r="H14" s="3">
-        <v>-156200</v>
+        <v>-174800</v>
       </c>
       <c r="I14" s="3">
-        <v>-460600</v>
+        <v>2276300</v>
       </c>
       <c r="J14" s="3">
-        <v>-1030100</v>
+        <v>-4499600</v>
       </c>
       <c r="K14" s="3">
         <v>1215800</v>
@@ -1021,25 +1019,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>116800</v>
+        <v>621600</v>
       </c>
       <c r="E15" s="3">
-        <v>123300</v>
+        <v>600000</v>
       </c>
       <c r="F15" s="3">
-        <v>91900</v>
+        <v>719000</v>
       </c>
       <c r="G15" s="3">
-        <v>734800</v>
+        <v>824600</v>
       </c>
       <c r="H15" s="3">
-        <v>148300</v>
+        <v>780100</v>
       </c>
       <c r="I15" s="3">
-        <v>149600</v>
+        <v>819500</v>
       </c>
       <c r="J15" s="3">
-        <v>195500</v>
+        <v>708300</v>
       </c>
       <c r="K15" s="3">
         <v>182400</v>
@@ -1082,25 +1080,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19080700</v>
+        <v>18665600</v>
       </c>
       <c r="E17" s="3">
-        <v>16536300</v>
+        <v>15380400</v>
       </c>
       <c r="F17" s="3">
-        <v>13973600</v>
+        <v>14560200</v>
       </c>
       <c r="G17" s="3">
-        <v>17684500</v>
+        <v>16210200</v>
       </c>
       <c r="H17" s="3">
-        <v>22701100</v>
+        <v>23203800</v>
       </c>
       <c r="I17" s="3">
-        <v>21693300</v>
+        <v>21502400</v>
       </c>
       <c r="J17" s="3">
-        <v>17840700</v>
+        <v>19308000</v>
       </c>
       <c r="K17" s="3">
         <v>18502300</v>
@@ -1127,25 +1125,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2552200</v>
+        <v>2333500</v>
       </c>
       <c r="E18" s="3">
-        <v>1204600</v>
+        <v>909700</v>
       </c>
       <c r="F18" s="3">
-        <v>746600</v>
+        <v>629600</v>
       </c>
       <c r="G18" s="3">
-        <v>-2606000</v>
+        <v>-521500</v>
       </c>
       <c r="H18" s="3">
-        <v>-935600</v>
+        <v>-1235700</v>
       </c>
       <c r="I18" s="3">
-        <v>-1053700</v>
+        <v>-1455500</v>
       </c>
       <c r="J18" s="3">
-        <v>1510300</v>
+        <v>624500</v>
       </c>
       <c r="K18" s="3">
         <v>50900</v>
@@ -1191,25 +1189,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1116700</v>
+        <v>-378300</v>
       </c>
       <c r="E20" s="3">
-        <v>-2725400</v>
+        <v>454200</v>
       </c>
       <c r="F20" s="3">
-        <v>-801800</v>
+        <v>43300</v>
       </c>
       <c r="G20" s="3">
-        <v>-833200</v>
+        <v>416400</v>
       </c>
       <c r="H20" s="3">
-        <v>5200</v>
+        <v>-62200</v>
       </c>
       <c r="I20" s="3">
-        <v>-2673000</v>
+        <v>-77700</v>
       </c>
       <c r="J20" s="3">
-        <v>3692500</v>
+        <v>-220300</v>
       </c>
       <c r="K20" s="3">
         <v>-5706800</v>
@@ -1236,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5019300</v>
+        <v>3333400</v>
       </c>
       <c r="E21" s="3">
-        <v>-203300</v>
+        <v>1055500</v>
       </c>
       <c r="F21" s="3">
-        <v>1269000</v>
+        <v>1305300</v>
       </c>
       <c r="G21" s="3">
-        <v>-217600</v>
+        <v>-113300</v>
       </c>
       <c r="H21" s="3">
-        <v>795300</v>
+        <v>-393400</v>
       </c>
       <c r="I21" s="3">
-        <v>-2543000</v>
+        <v>-558200</v>
       </c>
       <c r="J21" s="3">
-        <v>6235700</v>
+        <v>1553000</v>
       </c>
       <c r="K21" s="3">
         <v>-4625200</v>
@@ -1281,25 +1279,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>484200</v>
+        <v>468700</v>
       </c>
       <c r="E22" s="3">
-        <v>450100</v>
+        <v>184300</v>
       </c>
       <c r="F22" s="3">
-        <v>330700</v>
+        <v>341200</v>
       </c>
       <c r="G22" s="3">
-        <v>233600</v>
+        <v>345400</v>
       </c>
       <c r="H22" s="3">
-        <v>238800</v>
+        <v>222500</v>
       </c>
       <c r="I22" s="3">
-        <v>140400</v>
+        <v>136400</v>
       </c>
       <c r="J22" s="3">
-        <v>87900</v>
+        <v>90600</v>
       </c>
       <c r="K22" s="3">
         <v>95500</v>
@@ -1326,25 +1324,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3184700</v>
+        <v>3091400</v>
       </c>
       <c r="E23" s="3">
-        <v>-1970900</v>
+        <v>-1809700</v>
       </c>
       <c r="F23" s="3">
-        <v>-385800</v>
+        <v>-398100</v>
       </c>
       <c r="G23" s="3">
-        <v>-3672800</v>
+        <v>-3821500</v>
       </c>
       <c r="H23" s="3">
-        <v>-1169200</v>
+        <v>-1180100</v>
       </c>
       <c r="I23" s="3">
-        <v>-3867100</v>
+        <v>-3756000</v>
       </c>
       <c r="J23" s="3">
-        <v>5115000</v>
+        <v>5268600</v>
       </c>
       <c r="K23" s="3">
         <v>-5751400</v>
@@ -1371,25 +1369,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>30200</v>
+        <v>29300</v>
       </c>
       <c r="E24" s="3">
-        <v>-404200</v>
+        <v>-371100</v>
       </c>
       <c r="F24" s="3">
-        <v>-548500</v>
+        <v>-566000</v>
       </c>
       <c r="G24" s="3">
-        <v>396300</v>
+        <v>412300</v>
       </c>
       <c r="H24" s="3">
-        <v>551100</v>
+        <v>556300</v>
       </c>
       <c r="I24" s="3">
-        <v>-670500</v>
+        <v>-706100</v>
       </c>
       <c r="J24" s="3">
-        <v>610200</v>
+        <v>696100</v>
       </c>
       <c r="K24" s="3">
         <v>-749300</v>
@@ -1461,25 +1459,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3154500</v>
+        <v>3062100</v>
       </c>
       <c r="E26" s="3">
-        <v>-1566800</v>
+        <v>-1438600</v>
       </c>
       <c r="F26" s="3">
-        <v>162700</v>
+        <v>167900</v>
       </c>
       <c r="G26" s="3">
-        <v>-4069100</v>
+        <v>-4233800</v>
       </c>
       <c r="H26" s="3">
-        <v>-1720300</v>
+        <v>-1736300</v>
       </c>
       <c r="I26" s="3">
-        <v>-3196500</v>
+        <v>-3049900</v>
       </c>
       <c r="J26" s="3">
-        <v>4504800</v>
+        <v>4572500</v>
       </c>
       <c r="K26" s="3">
         <v>-5002100</v>
@@ -1506,25 +1504,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3165000</v>
+        <v>3072300</v>
       </c>
       <c r="E27" s="3">
-        <v>-1560200</v>
+        <v>-1529000</v>
       </c>
       <c r="F27" s="3">
-        <v>161400</v>
+        <v>162500</v>
       </c>
       <c r="G27" s="3">
-        <v>-4070400</v>
+        <v>-4328000</v>
       </c>
       <c r="H27" s="3">
-        <v>-1725500</v>
+        <v>-1741600</v>
       </c>
       <c r="I27" s="3">
-        <v>-3207000</v>
+        <v>-3060100</v>
       </c>
       <c r="J27" s="3">
-        <v>4503500</v>
+        <v>4571200</v>
       </c>
       <c r="K27" s="3">
         <v>-5002100</v>
@@ -1599,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-105000</v>
+        <v>-96400</v>
       </c>
       <c r="F29" s="3">
-        <v>-3900</v>
+        <v>-4100</v>
       </c>
       <c r="G29" s="3">
-        <v>-89200</v>
+        <v>-92800</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>56400</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-65600</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1731,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1116700</v>
+        <v>378300</v>
       </c>
       <c r="E32" s="3">
-        <v>2725400</v>
+        <v>-454200</v>
       </c>
       <c r="F32" s="3">
-        <v>801800</v>
+        <v>-43300</v>
       </c>
       <c r="G32" s="3">
-        <v>833200</v>
+        <v>-416400</v>
       </c>
       <c r="H32" s="3">
-        <v>-5200</v>
+        <v>62200</v>
       </c>
       <c r="I32" s="3">
-        <v>2673000</v>
+        <v>77700</v>
       </c>
       <c r="J32" s="3">
-        <v>-3692500</v>
+        <v>220300</v>
       </c>
       <c r="K32" s="3">
         <v>5706800</v>
@@ -1776,25 +1774,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3165000</v>
+        <v>3072300</v>
       </c>
       <c r="E33" s="3">
-        <v>-1665200</v>
+        <v>-1529000</v>
       </c>
       <c r="F33" s="3">
-        <v>157500</v>
+        <v>162500</v>
       </c>
       <c r="G33" s="3">
-        <v>-4159700</v>
+        <v>-4328000</v>
       </c>
       <c r="H33" s="3">
-        <v>-1725500</v>
+        <v>-1741600</v>
       </c>
       <c r="I33" s="3">
-        <v>-3150600</v>
+        <v>-3060100</v>
       </c>
       <c r="J33" s="3">
-        <v>4437900</v>
+        <v>4571200</v>
       </c>
       <c r="K33" s="3">
         <v>-5002100</v>
@@ -1866,25 +1864,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3165000</v>
+        <v>3072300</v>
       </c>
       <c r="E35" s="3">
-        <v>-1665200</v>
+        <v>-1529000</v>
       </c>
       <c r="F35" s="3">
-        <v>157500</v>
+        <v>162500</v>
       </c>
       <c r="G35" s="3">
-        <v>-4159700</v>
+        <v>-4328000</v>
       </c>
       <c r="H35" s="3">
-        <v>-1725500</v>
+        <v>-1741600</v>
       </c>
       <c r="I35" s="3">
-        <v>-3150600</v>
+        <v>-3060100</v>
       </c>
       <c r="J35" s="3">
-        <v>4437900</v>
+        <v>4571200</v>
       </c>
       <c r="K35" s="3">
         <v>-5002100</v>
@@ -1999,25 +1997,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2016900</v>
+        <v>4819900</v>
       </c>
       <c r="E41" s="3">
-        <v>847700</v>
+        <v>3141200</v>
       </c>
       <c r="F41" s="3">
-        <v>990700</v>
+        <v>3549000</v>
       </c>
       <c r="G41" s="3">
-        <v>1923700</v>
+        <v>4713000</v>
       </c>
       <c r="H41" s="3">
-        <v>2474800</v>
+        <v>5884400</v>
       </c>
       <c r="I41" s="3">
-        <v>2905200</v>
+        <v>6339500</v>
       </c>
       <c r="J41" s="3">
-        <v>5717300</v>
+        <v>3991300</v>
       </c>
       <c r="K41" s="3">
         <v>5162100</v>
@@ -2044,25 +2042,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2582400</v>
+        <v>10200</v>
       </c>
       <c r="E42" s="3">
-        <v>2279300</v>
+        <v>15700</v>
       </c>
       <c r="F42" s="3">
-        <v>2342300</v>
+        <v>10800</v>
       </c>
       <c r="G42" s="3">
-        <v>2418400</v>
+        <v>57300</v>
       </c>
       <c r="H42" s="3">
-        <v>3334300</v>
+        <v>72800</v>
       </c>
       <c r="I42" s="3">
-        <v>3588900</v>
+        <v>12700</v>
       </c>
       <c r="J42" s="3">
-        <v>2006400</v>
+        <v>4100</v>
       </c>
       <c r="K42" s="3">
         <v>1674800</v>
@@ -2089,25 +2087,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9021400</v>
+        <v>8757100</v>
       </c>
       <c r="E43" s="3">
-        <v>8773400</v>
+        <v>8055900</v>
       </c>
       <c r="F43" s="3">
-        <v>7797100</v>
+        <v>8045800</v>
       </c>
       <c r="G43" s="3">
-        <v>8113300</v>
+        <v>8441600</v>
       </c>
       <c r="H43" s="3">
-        <v>8654000</v>
+        <v>8674900</v>
       </c>
       <c r="I43" s="3">
-        <v>8119900</v>
+        <v>8109800</v>
       </c>
       <c r="J43" s="3">
-        <v>16334300</v>
+        <v>8185400</v>
       </c>
       <c r="K43" s="3">
         <v>15320200</v>
@@ -2134,25 +2132,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6361500</v>
+        <v>6175200</v>
       </c>
       <c r="E44" s="3">
-        <v>6177800</v>
+        <v>5672600</v>
       </c>
       <c r="F44" s="3">
-        <v>4810500</v>
+        <v>4964000</v>
       </c>
       <c r="G44" s="3">
-        <v>4842000</v>
+        <v>5038000</v>
       </c>
       <c r="H44" s="3">
-        <v>5668700</v>
+        <v>5721500</v>
       </c>
       <c r="I44" s="3">
-        <v>5625400</v>
+        <v>5463900</v>
       </c>
       <c r="J44" s="3">
-        <v>10103900</v>
+        <v>5140200</v>
       </c>
       <c r="K44" s="3">
         <v>7988200</v>
@@ -2179,25 +2177,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3783100</v>
+        <v>319700</v>
       </c>
       <c r="E45" s="3">
-        <v>2931500</v>
+        <v>262700</v>
       </c>
       <c r="F45" s="3">
-        <v>1494600</v>
+        <v>2881400</v>
       </c>
       <c r="G45" s="3">
-        <v>1507700</v>
+        <v>566600</v>
       </c>
       <c r="H45" s="3">
-        <v>934300</v>
+        <v>132400</v>
       </c>
       <c r="I45" s="3">
-        <v>1831800</v>
+        <v>1032400</v>
       </c>
       <c r="J45" s="3">
-        <v>359500</v>
+        <v>127100</v>
       </c>
       <c r="K45" s="3">
         <v>299000</v>
@@ -2224,25 +2222,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>23765300</v>
+        <v>23207800</v>
       </c>
       <c r="E46" s="3">
-        <v>21009600</v>
+        <v>19291500</v>
       </c>
       <c r="F46" s="3">
-        <v>17435200</v>
+        <v>20737400</v>
       </c>
       <c r="G46" s="3">
-        <v>18805100</v>
+        <v>19959300</v>
       </c>
       <c r="H46" s="3">
-        <v>21066100</v>
+        <v>21286000</v>
       </c>
       <c r="I46" s="3">
-        <v>22071200</v>
+        <v>21437400</v>
       </c>
       <c r="J46" s="3">
-        <v>17212100</v>
+        <v>17729300</v>
       </c>
       <c r="K46" s="3">
         <v>14548500</v>
@@ -2269,25 +2267,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>669200</v>
+        <v>973100</v>
       </c>
       <c r="E47" s="3">
-        <v>601000</v>
+        <v>1077200</v>
       </c>
       <c r="F47" s="3">
-        <v>577400</v>
+        <v>834100</v>
       </c>
       <c r="G47" s="3">
-        <v>541900</v>
+        <v>916100</v>
       </c>
       <c r="H47" s="3">
-        <v>566900</v>
+        <v>819800</v>
       </c>
       <c r="I47" s="3">
-        <v>569500</v>
+        <v>925300</v>
       </c>
       <c r="J47" s="3">
-        <v>526200</v>
+        <v>855600</v>
       </c>
       <c r="K47" s="3">
         <v>735700</v>
@@ -2314,25 +2312,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6079400</v>
+        <v>5901300</v>
       </c>
       <c r="E48" s="3">
-        <v>6557100</v>
+        <v>6020800</v>
       </c>
       <c r="F48" s="3">
-        <v>6718500</v>
+        <v>6932800</v>
       </c>
       <c r="G48" s="3">
-        <v>7768200</v>
+        <v>8082600</v>
       </c>
       <c r="H48" s="3">
-        <v>8938700</v>
+        <v>9021900</v>
       </c>
       <c r="I48" s="3">
-        <v>6467800</v>
+        <v>6282100</v>
       </c>
       <c r="J48" s="3">
-        <v>6112200</v>
+        <v>6295900</v>
       </c>
       <c r="K48" s="3">
         <v>10232500</v>
@@ -2359,25 +2357,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5260600</v>
+        <v>2240500</v>
       </c>
       <c r="E49" s="3">
-        <v>5377400</v>
+        <v>2311000</v>
       </c>
       <c r="F49" s="3">
-        <v>5302600</v>
+        <v>2572700</v>
       </c>
       <c r="G49" s="3">
-        <v>6751300</v>
+        <v>3891100</v>
       </c>
       <c r="H49" s="3">
-        <v>7141000</v>
+        <v>3680600</v>
       </c>
       <c r="I49" s="3">
-        <v>6948100</v>
+        <v>3757300</v>
       </c>
       <c r="J49" s="3">
-        <v>7302400</v>
+        <v>4829400</v>
       </c>
       <c r="K49" s="3">
         <v>11408600</v>
@@ -2494,25 +2492,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5575500</v>
+        <v>1131100</v>
       </c>
       <c r="E52" s="3">
-        <v>5099200</v>
+        <v>866300</v>
       </c>
       <c r="F52" s="3">
-        <v>7592400</v>
+        <v>1805000</v>
       </c>
       <c r="G52" s="3">
-        <v>4865600</v>
+        <v>1824000</v>
       </c>
       <c r="H52" s="3">
-        <v>4626800</v>
+        <v>1899200</v>
       </c>
       <c r="I52" s="3">
-        <v>5746100</v>
+        <v>2542700</v>
       </c>
       <c r="J52" s="3">
-        <v>5492900</v>
+        <v>3383100</v>
       </c>
       <c r="K52" s="3">
         <v>4358200</v>
@@ -2584,25 +2582,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>41350000</v>
+        <v>40138600</v>
       </c>
       <c r="E54" s="3">
-        <v>38644300</v>
+        <v>35484100</v>
       </c>
       <c r="F54" s="3">
-        <v>37626000</v>
+        <v>38826300</v>
       </c>
       <c r="G54" s="3">
-        <v>38732200</v>
+        <v>40299500</v>
       </c>
       <c r="H54" s="3">
-        <v>42339400</v>
+        <v>42733600</v>
       </c>
       <c r="I54" s="3">
-        <v>41802800</v>
+        <v>40602300</v>
       </c>
       <c r="J54" s="3">
-        <v>36645800</v>
+        <v>37746800</v>
       </c>
       <c r="K54" s="3">
         <v>29877400</v>
@@ -2667,25 +2665,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2821200</v>
+        <v>2738600</v>
       </c>
       <c r="E57" s="3">
-        <v>3020700</v>
+        <v>2773700</v>
       </c>
       <c r="F57" s="3">
-        <v>2306800</v>
+        <v>2380400</v>
       </c>
       <c r="G57" s="3">
-        <v>2625700</v>
+        <v>2732000</v>
       </c>
       <c r="H57" s="3">
-        <v>4065200</v>
+        <v>3737500</v>
       </c>
       <c r="I57" s="3">
-        <v>4140000</v>
+        <v>4021100</v>
       </c>
       <c r="J57" s="3">
-        <v>17990300</v>
+        <v>2780300</v>
       </c>
       <c r="K57" s="3">
         <v>10398700</v>
@@ -2712,25 +2710,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1061600</v>
+        <v>1076300</v>
       </c>
       <c r="E58" s="3">
-        <v>469800</v>
+        <v>462700</v>
       </c>
       <c r="F58" s="3">
-        <v>366100</v>
+        <v>411600</v>
       </c>
       <c r="G58" s="3">
-        <v>1669100</v>
+        <v>1789900</v>
       </c>
       <c r="H58" s="3">
-        <v>1017000</v>
+        <v>1067500</v>
       </c>
       <c r="I58" s="3">
-        <v>1125900</v>
+        <v>1130500</v>
       </c>
       <c r="J58" s="3">
-        <v>215200</v>
+        <v>148700</v>
       </c>
       <c r="K58" s="3">
         <v>426800</v>
@@ -2757,25 +2755,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15703100</v>
+        <v>13635600</v>
       </c>
       <c r="E59" s="3">
-        <v>14772700</v>
+        <v>11647700</v>
       </c>
       <c r="F59" s="3">
-        <v>11969900</v>
+        <v>10420800</v>
       </c>
       <c r="G59" s="3">
-        <v>13682300</v>
+        <v>12515700</v>
       </c>
       <c r="H59" s="3">
-        <v>14569400</v>
+        <v>12612400</v>
       </c>
       <c r="I59" s="3">
-        <v>14221600</v>
+        <v>11963900</v>
       </c>
       <c r="J59" s="3">
-        <v>19487500</v>
+        <v>11740200</v>
       </c>
       <c r="K59" s="3">
         <v>13970400</v>
@@ -2802,25 +2800,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>19585900</v>
+        <v>19012100</v>
       </c>
       <c r="E60" s="3">
-        <v>18263200</v>
+        <v>16769700</v>
       </c>
       <c r="F60" s="3">
-        <v>14642800</v>
+        <v>15109900</v>
       </c>
       <c r="G60" s="3">
-        <v>17977100</v>
+        <v>19015900</v>
       </c>
       <c r="H60" s="3">
-        <v>19651500</v>
+        <v>19854300</v>
       </c>
       <c r="I60" s="3">
-        <v>19487500</v>
+        <v>19407100</v>
       </c>
       <c r="J60" s="3">
-        <v>16312000</v>
+        <v>16802100</v>
       </c>
       <c r="K60" s="3">
         <v>13903400</v>
@@ -2847,25 +2845,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6495400</v>
+        <v>6398100</v>
       </c>
       <c r="E61" s="3">
-        <v>7344400</v>
+        <v>6861900</v>
       </c>
       <c r="F61" s="3">
-        <v>9837600</v>
+        <v>10262400</v>
       </c>
       <c r="G61" s="3">
-        <v>7949300</v>
+        <v>8425300</v>
       </c>
       <c r="H61" s="3">
-        <v>6442900</v>
+        <v>6514800</v>
       </c>
       <c r="I61" s="3">
-        <v>4991600</v>
+        <v>4853400</v>
       </c>
       <c r="J61" s="3">
-        <v>4469400</v>
+        <v>4610400</v>
       </c>
       <c r="K61" s="3">
         <v>3951300</v>
@@ -2892,25 +2890,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19958600</v>
+        <v>6795500</v>
       </c>
       <c r="E62" s="3">
-        <v>20930900</v>
+        <v>8622200</v>
       </c>
       <c r="F62" s="3">
-        <v>18280300</v>
+        <v>8123000</v>
       </c>
       <c r="G62" s="3">
-        <v>18903600</v>
+        <v>8066200</v>
       </c>
       <c r="H62" s="3">
-        <v>20626500</v>
+        <v>9312000</v>
       </c>
       <c r="I62" s="3">
-        <v>18210700</v>
+        <v>7886700</v>
       </c>
       <c r="J62" s="3">
-        <v>23142000</v>
+        <v>6764900</v>
       </c>
       <c r="K62" s="3">
         <v>25849100</v>
@@ -3072,25 +3070,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>46180300</v>
+        <v>44761000</v>
       </c>
       <c r="E66" s="3">
-        <v>46583100</v>
+        <v>42732700</v>
       </c>
       <c r="F66" s="3">
-        <v>43743500</v>
+        <v>45103700</v>
       </c>
       <c r="G66" s="3">
-        <v>45158100</v>
+        <v>46955400</v>
       </c>
       <c r="H66" s="3">
-        <v>46769400</v>
+        <v>47175700</v>
       </c>
       <c r="I66" s="3">
-        <v>43212100</v>
+        <v>41943100</v>
       </c>
       <c r="J66" s="3">
-        <v>35425500</v>
+        <v>36485800</v>
       </c>
       <c r="K66" s="3">
         <v>33052100</v>
@@ -3316,25 +3314,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-9215600</v>
+        <v>-9186300</v>
       </c>
       <c r="E72" s="3">
-        <v>-12627300</v>
+        <v>-11827200</v>
       </c>
       <c r="F72" s="3">
-        <v>-10031800</v>
+        <v>-11543400</v>
       </c>
       <c r="G72" s="3">
-        <v>-10514700</v>
+        <v>-12170300</v>
       </c>
       <c r="H72" s="3">
-        <v>-5750100</v>
+        <v>-7018100</v>
       </c>
       <c r="I72" s="3">
-        <v>-3180800</v>
+        <v>-3968900</v>
       </c>
       <c r="J72" s="3">
-        <v>632500</v>
+        <v>-533900</v>
       </c>
       <c r="K72" s="3">
         <v>-3690800</v>
@@ -3496,25 +3494,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-4830200</v>
+        <v>-4688700</v>
       </c>
       <c r="E76" s="3">
-        <v>-7938800</v>
+        <v>-7289600</v>
       </c>
       <c r="F76" s="3">
-        <v>-6117500</v>
+        <v>-6312600</v>
       </c>
       <c r="G76" s="3">
-        <v>-6425800</v>
+        <v>-6685900</v>
       </c>
       <c r="H76" s="3">
-        <v>-4430000</v>
+        <v>-4471200</v>
       </c>
       <c r="I76" s="3">
-        <v>-1409300</v>
+        <v>-1368800</v>
       </c>
       <c r="J76" s="3">
-        <v>1220300</v>
+        <v>1257000</v>
       </c>
       <c r="K76" s="3">
         <v>-3174700</v>
@@ -3636,25 +3634,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3165000</v>
+        <v>3072300</v>
       </c>
       <c r="E81" s="3">
-        <v>-1665200</v>
+        <v>-1529000</v>
       </c>
       <c r="F81" s="3">
-        <v>157500</v>
+        <v>162500</v>
       </c>
       <c r="G81" s="3">
-        <v>-4159700</v>
+        <v>-4328000</v>
       </c>
       <c r="H81" s="3">
-        <v>-1725500</v>
+        <v>-1741600</v>
       </c>
       <c r="I81" s="3">
-        <v>-3150600</v>
+        <v>-3060100</v>
       </c>
       <c r="J81" s="3">
-        <v>4437900</v>
+        <v>4571200</v>
       </c>
       <c r="K81" s="3">
         <v>-5002100</v>
@@ -3700,25 +3698,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1350300</v>
+        <v>852100</v>
       </c>
       <c r="E83" s="3">
-        <v>1317400</v>
+        <v>843400</v>
       </c>
       <c r="F83" s="3">
-        <v>1324000</v>
+        <v>968200</v>
       </c>
       <c r="G83" s="3">
-        <v>3221500</v>
+        <v>1140000</v>
       </c>
       <c r="H83" s="3">
-        <v>1725500</v>
+        <v>1178700</v>
       </c>
       <c r="I83" s="3">
-        <v>1183600</v>
+        <v>655100</v>
       </c>
       <c r="J83" s="3">
-        <v>1032700</v>
+        <v>600100</v>
       </c>
       <c r="K83" s="3">
         <v>1029700</v>
@@ -3970,25 +3968,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3260800</v>
+        <v>3165300</v>
       </c>
       <c r="E89" s="3">
-        <v>2427600</v>
+        <v>1836300</v>
       </c>
       <c r="F89" s="3">
-        <v>-339900</v>
+        <v>-350700</v>
       </c>
       <c r="G89" s="3">
-        <v>-3948400</v>
+        <v>-4108200</v>
       </c>
       <c r="H89" s="3">
-        <v>3014100</v>
+        <v>3042200</v>
       </c>
       <c r="I89" s="3">
-        <v>2921000</v>
+        <v>2837100</v>
       </c>
       <c r="J89" s="3">
-        <v>1984000</v>
+        <v>2043700</v>
       </c>
       <c r="K89" s="3">
         <v>1750500</v>
@@ -4034,25 +4032,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-562900</v>
+        <v>-546400</v>
       </c>
       <c r="E91" s="3">
-        <v>-471100</v>
+        <v>-432600</v>
       </c>
       <c r="F91" s="3">
-        <v>-430400</v>
+        <v>-444100</v>
       </c>
       <c r="G91" s="3">
-        <v>-767600</v>
+        <v>-798700</v>
       </c>
       <c r="H91" s="3">
-        <v>-980200</v>
+        <v>-989300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1187500</v>
+        <v>-1153400</v>
       </c>
       <c r="J91" s="3">
-        <v>-957900</v>
+        <v>-986700</v>
       </c>
       <c r="K91" s="3">
         <v>-725800</v>
@@ -4169,25 +4167,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-952700</v>
+        <v>-924700</v>
       </c>
       <c r="E94" s="3">
-        <v>1083900</v>
+        <v>995200</v>
       </c>
       <c r="F94" s="3">
-        <v>-561600</v>
+        <v>-579500</v>
       </c>
       <c r="G94" s="3">
-        <v>-1325300</v>
+        <v>-1379000</v>
       </c>
       <c r="H94" s="3">
-        <v>-1204600</v>
+        <v>-1215800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1279400</v>
+        <v>-1242700</v>
       </c>
       <c r="J94" s="3">
-        <v>-1514300</v>
+        <v>-1559800</v>
       </c>
       <c r="K94" s="3">
         <v>-1690900</v>
@@ -4233,25 +4231,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>124200</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>291400</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>275300</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>289200</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4413,25 +4411,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-720400</v>
+        <v>-699300</v>
       </c>
       <c r="E100" s="3">
-        <v>-3760800</v>
+        <v>-3060400</v>
       </c>
       <c r="F100" s="3">
-        <v>-115500</v>
+        <v>-119200</v>
       </c>
       <c r="G100" s="3">
-        <v>3968100</v>
+        <v>4128700</v>
       </c>
       <c r="H100" s="3">
-        <v>-2351500</v>
+        <v>-2373400</v>
       </c>
       <c r="I100" s="3">
-        <v>921200</v>
+        <v>894700</v>
       </c>
       <c r="J100" s="3">
-        <v>-166600</v>
+        <v>-171700</v>
       </c>
       <c r="K100" s="3">
         <v>-916800</v>
@@ -4458,25 +4456,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-110200</v>
+        <v>-107000</v>
       </c>
       <c r="E101" s="3">
-        <v>204700</v>
+        <v>188000</v>
       </c>
       <c r="F101" s="3">
-        <v>-107600</v>
+        <v>-111000</v>
       </c>
       <c r="G101" s="3">
-        <v>73500</v>
+        <v>76500</v>
       </c>
       <c r="H101" s="3">
-        <v>-136500</v>
+        <v>-137700</v>
       </c>
       <c r="I101" s="3">
-        <v>86600</v>
+        <v>84100</v>
       </c>
       <c r="J101" s="3">
-        <v>-90500</v>
+        <v>-93300</v>
       </c>
       <c r="K101" s="3">
         <v>354800</v>
@@ -4503,25 +4501,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1477500</v>
+        <v>1434200</v>
       </c>
       <c r="E102" s="3">
-        <v>-44600</v>
+        <v>-41000</v>
       </c>
       <c r="F102" s="3">
-        <v>-1124600</v>
+        <v>-1160400</v>
       </c>
       <c r="G102" s="3">
-        <v>-1232200</v>
+        <v>-1282000</v>
       </c>
       <c r="H102" s="3">
-        <v>-678400</v>
+        <v>-684700</v>
       </c>
       <c r="I102" s="3">
-        <v>2649300</v>
+        <v>2573300</v>
       </c>
       <c r="J102" s="3">
-        <v>212600</v>
+        <v>219000</v>
       </c>
       <c r="K102" s="3">
         <v>-502400</v>

--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23672600</v>
+      </c>
+      <c r="E8" s="3">
         <v>20999100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16290100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15189800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15688700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21968100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20046900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19932400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18553200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16076100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17906100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20106200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15721900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14648000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18372000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16355000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13053800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12297600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14169100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20720500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18520000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16658800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14771800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12250600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13730700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32486900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12193800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11424500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5300600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4644100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3236300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2892300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1519600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1247600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1526900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3273600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3781300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3825500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4175400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-12380700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3528100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3223500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,53 +890,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>749900</v>
+      </c>
+      <c r="E12" s="3">
         <v>941300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1073600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1053500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>987100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1019800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>978800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1139400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>956500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>797700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>870800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1658800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1447900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>609700</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -967,99 +983,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>408100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-639400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2123000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>652700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2566800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-174800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2276300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4499600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1215800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-473800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-903700</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>537100</v>
+      </c>
+      <c r="E15" s="3">
         <v>621600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>600000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>719000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>824600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>780100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>819500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>708300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>182400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>160500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>162900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>178500</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20644200</v>
+      </c>
+      <c r="E17" s="3">
         <v>18665600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15380400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14560200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16210200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23203800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21502400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19308000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18502300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14318000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16103200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17655100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13036700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13086300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3028400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2333500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>909700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>629600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-521500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1235700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1455500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>624500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1758100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1802900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2451100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2685200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1561700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,233 +1215,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-242900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-378300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>454200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>43300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>416400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-62200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-77700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-220300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5706800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1487600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1633400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-37100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>956700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-39500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3808400</v>
+      </c>
+      <c r="E21" s="3">
         <v>3333400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1055500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1305300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-113300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-393400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-558200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1553000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4625200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1156300</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3">
         <v>4274900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2060100</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>403100</v>
+      </c>
+      <c r="E22" s="3">
         <v>468700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>184300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>341200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>345400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>222500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>136400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>90600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>95500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>83200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>82100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>79600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>65900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>67200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2796800</v>
+      </c>
+      <c r="E23" s="3">
         <v>3091400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1809700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-398100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3821500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1180100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3756000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5268600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5751400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>187400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>87300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2334400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3575900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1455100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-313000</v>
+      </c>
+      <c r="E24" s="3">
         <v>29300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-371100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-566000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>412300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>556300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-706100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>696100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-749300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>89000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>196800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>517700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>557200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>338400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3109800</v>
+      </c>
+      <c r="E26" s="3">
         <v>3062100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1438600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>167900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4233800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1736300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3049900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4572500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5002100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>98400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-109500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1816700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3018700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1116600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3156100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3072300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1529000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>162500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4328000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1741600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3060100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4571200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5002100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>97200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-95200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1119300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,9 +1644,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1597,44 +1657,47 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-96400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-4100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-92800</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>185100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>76900</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>242900</v>
+      </c>
+      <c r="E32" s="3">
         <v>378300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-454200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-43300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-416400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>62200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>77700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>220300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5706800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1487600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1633400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>37100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-956700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>39500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3156100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3072300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1529000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>162500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4328000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1741600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3060100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4571200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5002100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>97200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>89900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1877200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3000600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1119300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3156100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3072300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1529000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>162500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4328000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1741600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3060100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4571200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5002100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>97200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>89900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1877200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3000600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1119300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,413 +2076,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6979500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4819900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3141200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3549000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4713000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5884400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6339500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3991300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5162100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1667900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4112800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5086300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8082600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1706600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E42" s="3">
         <v>10200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>57300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>72800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1674800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2029900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>440800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1971500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>32900</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9860200</v>
+      </c>
+      <c r="E43" s="3">
         <v>8757100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8055900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8045800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8441600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8674900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8109800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8185400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15320200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7112100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7915400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6691600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15530500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5099900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6374800</v>
+      </c>
+      <c r="E44" s="3">
         <v>6175200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5672600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4964000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5038000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5721500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5463900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5140200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7988200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3088700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3437600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4557600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10572600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3372300</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>436900</v>
+      </c>
+      <c r="E45" s="3">
         <v>319700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>262700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2881400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>566600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>132400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1032400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>127100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>299000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>292800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>325900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>825300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>837700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>737400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27074100</v>
+      </c>
+      <c r="E46" s="3">
         <v>23207800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19291500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20737400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19959300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21286000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21437400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17729300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14548500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14191500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15794300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17601500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12401900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10949100</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>885100</v>
+      </c>
+      <c r="E47" s="3">
         <v>973100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1077200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>834100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>916100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>819800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>925300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>855600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>735700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>713300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>793900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>862400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4669600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2225400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5614900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5901300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6020800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6932800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8082600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9021900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6282100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6295900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10232500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4087800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4549500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4657900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9944300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3078700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2048100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2240500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2311000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2572700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3891100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3680600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3757300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4829400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11408600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5440700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6055200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6848100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11251300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3795000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2601,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1009100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1131100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>866300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1805000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1824000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1899200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2542700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3383100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4358200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1714800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1908500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1700000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3248800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1577500</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44676200</v>
+      </c>
+      <c r="E54" s="3">
         <v>40138600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>35484100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38826300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>40299500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42733600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40602300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37746800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29877400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26148100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29101300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31669900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23459300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21625600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,278 +2788,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2526400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2738600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2773700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2380400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2732000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3737500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4021100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2780300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10398700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1867100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2077900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2143500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14007600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3773900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1402200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1076300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>462700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>411600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1789900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1067500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1130500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>148700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>426800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>490800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>546200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>284300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>385300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>26300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13795000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13635600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11647700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10420800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12515700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12612400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11963900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11740200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13970400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7215200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8030100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11002000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12483400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5306700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20986000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19012100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16769700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15109900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19015900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19854300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19407100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16802100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13903400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9573000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10654200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13429800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9318600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9106900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5190500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6398100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6861900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10262400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8425300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6514800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4853400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4610400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3951300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3376900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3758200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3465900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2135700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1559100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6228300</v>
+      </c>
+      <c r="E62" s="3">
         <v>6795500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8622200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8123000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8066200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9312000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7886700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6764900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25849100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7323000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8150000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6118900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8779500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5009100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45779100</v>
+      </c>
+      <c r="E66" s="3">
         <v>44761000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42732700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45103700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46955400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47175700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41943100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36485800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33052100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20275200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22565100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23973200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15729600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15676400</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3262,9 +3429,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5552300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9186300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11827200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11543400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12170300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7018100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3968900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-533900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3690800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5349300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5953500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7163900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14793600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5456800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1141800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-4688700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-7289600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-6312600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-6685900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4471200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1368800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1257000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3174700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5872900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6536200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7696700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7729700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5949300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3156100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3072300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1529000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>162500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4328000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1741600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3060100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4571200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5002100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>97200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>89900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1877200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3000600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1119300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>791200</v>
+      </c>
+      <c r="E83" s="3">
         <v>852100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>843400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>968200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1140000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1178700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>655100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1029700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>913600</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P83" s="3">
         <v>629600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>539900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4734800</v>
+      </c>
+      <c r="E89" s="3">
         <v>3165300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1836300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-350700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4108200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3042200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2837100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2043700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1750500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1281400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1696000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2801300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1622500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1719700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-649700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-546400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-432600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-444100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-798700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-989300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1153400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-986700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-725800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-570400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-844700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-918700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-562400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1020500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1040300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-924700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>995200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-579500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1379000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1215800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1242700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1559800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1690900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1165400</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P94" s="3">
         <v>548200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2906200</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,8 +4457,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4234,26 +4467,26 @@
         <v>1300</v>
       </c>
       <c r="E96" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F96" s="3">
         <v>1200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>124200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>291400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>275300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>289200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4269,9 +4502,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,142 +4646,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1310800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-699300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3060400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-119200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4128700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2373400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>894700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-171700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-916800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>258900</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P100" s="3">
         <v>-427900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-862500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-107000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>188000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-111000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>76500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-137700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>84100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-93300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>354800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P101" s="3">
         <v>-69800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2306000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1434200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1160400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1282000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-684700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2573300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>219000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-502400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>367800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1466500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1925200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1672900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2054200</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYCEY_YR_FIN.xlsx
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28542400</v>
+      </c>
+      <c r="E8" s="3">
         <v>23672600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20999100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16290100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15189800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15688700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21968100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20046900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19932400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18553200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16076100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17906100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20106200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15721900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14648000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20588200</v>
+      </c>
+      <c r="E9" s="3">
         <v>18372000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16355000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13053800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12297600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14169100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20720500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18520000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16658800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14771800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12250600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13730700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32486900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12193800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11424500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7954200</v>
+      </c>
+      <c r="E10" s="3">
         <v>5300600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4644100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3236300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2892300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1519600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1247600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1526900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3273600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3781300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3825500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4175400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-12380700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3528100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3223500</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,56 +903,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>674300</v>
+      </c>
+      <c r="E12" s="3">
         <v>749900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>941300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1073600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1053500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>987100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1019800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>978800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1139400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>956500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>797700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>870800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1658800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1447900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>609700</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,105 +1002,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>408100</v>
+        <v>-3169600</v>
       </c>
       <c r="E14" s="3">
-        <v>-639400</v>
+        <v>430700</v>
       </c>
       <c r="F14" s="3">
+        <v>-563000</v>
+      </c>
+      <c r="G14" s="3">
         <v>2123000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>652700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2566800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-174800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2276300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4499600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1215800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-473800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-903700</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>550500</v>
+      </c>
+      <c r="E15" s="3">
         <v>537100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>621600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>719000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>824600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>780100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>819500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>708300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>182400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>160500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>162900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>178500</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22905800</v>
+      </c>
+      <c r="E17" s="3">
         <v>20644200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18665600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15380400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14560200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16210200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23203800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21502400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19308000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18502300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14318000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16103200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17655100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13036700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13086300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5636600</v>
+      </c>
+      <c r="E18" s="3">
         <v>3028400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2333500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>909700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>629600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-521500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1235700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1455500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>624500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1758100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1802900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2451100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2685200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1561700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1216,248 +1248,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-242900</v>
+        <v>-574700</v>
       </c>
       <c r="E20" s="3">
-        <v>-378300</v>
+        <v>-265400</v>
       </c>
       <c r="F20" s="3">
+        <v>-454700</v>
+      </c>
+      <c r="G20" s="3">
         <v>454200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>43300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>416400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-62200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-77700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-220300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5706800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1487600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1633400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-37100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>956700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-39500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3808400</v>
+        <v>6761800</v>
       </c>
       <c r="E21" s="3">
-        <v>3333400</v>
+        <v>3830900</v>
       </c>
       <c r="F21" s="3">
+        <v>3409800</v>
+      </c>
+      <c r="G21" s="3">
         <v>1055500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1305300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-113300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-393400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-558200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1553000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4625200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1156300</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="3">
         <v>4274900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2060100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>411800</v>
+      </c>
+      <c r="E22" s="3">
         <v>403100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>468700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>184300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>341200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>345400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>222500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>136400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>90600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>95500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>83200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>82100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>79600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>65900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>67200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9333800</v>
+      </c>
+      <c r="E23" s="3">
         <v>2796800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3091400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1809700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-398100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3821500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1180100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3756000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5268600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5751400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>187400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>87300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2334400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3575900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1455100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1479100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-313000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-371100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-566000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>412300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>556300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-706100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>696100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-749300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>89000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>196800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>517700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>557200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>338400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7854600</v>
+      </c>
+      <c r="E26" s="3">
         <v>3109800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3062100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1438600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>167900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4233800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1736300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3049900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4572500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5002100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>98400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-109500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1816700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3018700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1116600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7861400</v>
+      </c>
+      <c r="E27" s="3">
         <v>3156100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3072300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1529000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>162500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4328000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1741600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3060100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4571200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5002100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>97200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-95200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3000600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1119300</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1647,9 +1704,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1660,44 +1720,47 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-96400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-4100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-92800</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>185100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>76900</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,105 +1857,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>242900</v>
+        <v>574700</v>
       </c>
       <c r="E32" s="3">
-        <v>378300</v>
+        <v>265400</v>
       </c>
       <c r="F32" s="3">
+        <v>454700</v>
+      </c>
+      <c r="G32" s="3">
         <v>-454200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-43300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-416400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>62200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>77700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>220300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5706800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1487600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1633400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>37100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-956700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>39500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7861400</v>
+      </c>
+      <c r="E33" s="3">
         <v>3156100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3072300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1529000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>162500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4328000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1741600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3060100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4571200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5002100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>97200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>89900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1877200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1119300</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7861400</v>
+      </c>
+      <c r="E35" s="3">
         <v>3156100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3072300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1529000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>162500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4328000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1741600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3060100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4571200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5002100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>97200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>89900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1877200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1119300</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,440 +2162,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8403800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6979500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4819900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3141200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3549000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4713000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5884400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6339500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3991300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5162100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1667900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4112800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5086300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8082600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1706600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E42" s="3">
         <v>185300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>57300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>72800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1674800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2029900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>440800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1971500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>32900</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10508700</v>
+      </c>
+      <c r="E43" s="3">
         <v>9860200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8757100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8055900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8045800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8441600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8674900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8109800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8185400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15320200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7112100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7915400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6691600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15530500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5099900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7709300</v>
+      </c>
+      <c r="E44" s="3">
         <v>6374800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6175200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5672600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4964000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5038000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5721500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5463900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5140200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7988200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3088700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3437600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4557600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10572600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3372300</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>632600</v>
+      </c>
+      <c r="E45" s="3">
         <v>436900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>319700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>262700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2881400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>566600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>132400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1032400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>127100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>299000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>292800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>325900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>825300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>837700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>737400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31207300</v>
+      </c>
+      <c r="E46" s="3">
         <v>27074100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23207800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19291500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20737400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19959300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21286000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21437400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17729300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14548500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14191500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15794300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17601500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12401900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10949100</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1777900</v>
+      </c>
+      <c r="E47" s="3">
         <v>885100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>973100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1077200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>834100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>916100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>819800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>925300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>855600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>735700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>713300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>793900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>862400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4669600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2225400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6422600</v>
+      </c>
+      <c r="E48" s="3">
         <v>5614900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5901300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6020800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6932800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8082600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9021900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6282100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6295900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10232500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4087800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4549500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4657900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9944300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3078700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2240900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2048100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2240500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2311000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2572700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3891100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3680600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3757300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4829400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11408600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5440700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6055200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6848100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11251300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3795000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,57 +2720,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1045800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1009100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1131100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>866300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1805000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1824000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1899200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2542700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3383100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4358200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1714800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1908500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1700000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3248800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1577500</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51298800</v>
+      </c>
+      <c r="E54" s="3">
         <v>44676200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40138600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35484100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38826300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40299500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42733600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40602300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37746800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29877400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26148100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29101300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31669900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23459300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21625600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,296 +2918,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3675600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2526400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2738600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2773700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2380400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2732000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3737500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4021100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2780300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10398700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1867100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2077900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2143500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14007600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3773900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1979800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1402200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1076300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>462700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>411600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1789900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1067500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1130500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>148700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>426800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>490800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>546200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>284300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>385300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17129200</v>
+      </c>
+      <c r="E59" s="3">
         <v>13795000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13635600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11647700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10420800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12515700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12612400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11963900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11740200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13970400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7215200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8030100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11002000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12483400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5306700</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25958300</v>
+      </c>
+      <c r="E60" s="3">
         <v>20986000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19012100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16769700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15109900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19015900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19854300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19407100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16802100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13903400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9573000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10654200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13429800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9318600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9106900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3891000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5190500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6398100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6861900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10262400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8425300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6514800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4853400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4610400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3951300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3376900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3758200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3465900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2135700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1559100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4570700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6228300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6795500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8622200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8123000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8066200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9312000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7886700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6764900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25849100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7323000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8150000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6118900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8779500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5009100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47593500</v>
+      </c>
+      <c r="E66" s="3">
         <v>45779100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44761000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42732700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45103700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46955400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47175700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>41943100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36485800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33052100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20275200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22565100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23973200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15729600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15676400</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5552300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9186300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11827200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11543400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12170300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7018100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3968900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-533900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3690800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5349300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5953500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7163900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14793600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5456800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3668900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1141800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-4688700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-7289600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-6312600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-6685900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4471200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1368800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1257000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-3174700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5872900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6536200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7696700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7729700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5949300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7861400</v>
+      </c>
+      <c r="E81" s="3">
         <v>3156100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3072300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1529000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>162500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4328000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1741600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3060100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4571200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5002100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>97200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>89900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1877200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1119300</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>897700</v>
+      </c>
+      <c r="E83" s="3">
         <v>791200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>852100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>843400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>968200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1140000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1178700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>655100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1029700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>913600</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q83" s="3">
         <v>629600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>539900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6144000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4734800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3165300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1836300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-350700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4108200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3042200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2837100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2043700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1750500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1281400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1696000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2801300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1622500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1719700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-835800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-649700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-546400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-432600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-444100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-798700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-989300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1153400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-986700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-725800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-570400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-844700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-918700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-562400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1020500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1263800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1040300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-924700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>995200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-579500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1379000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1215800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1242700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1559800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1690900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1165400</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q94" s="3">
         <v>548200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2906200</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,38 +4690,39 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>1300</v>
+        <v>1191100</v>
       </c>
       <c r="E96" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>1200</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>124200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>291400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>275300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>289200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4505,9 +4738,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,151 +4891,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4001300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1310800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-699300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3060400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-119200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4128700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2373400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>894700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-171700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-916800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>258900</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-427900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-862500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-77600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-107000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>188000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-111000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>76500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-137700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>84100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-93300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>354800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>899100</v>
+      </c>
+      <c r="E102" s="3">
         <v>2306000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1434200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-41000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1160400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1282000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-684700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2573300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>219000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-502400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>367800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1466500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1925200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1672900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2054200</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
